--- a/datosIntentosMedias.xlsx
+++ b/datosIntentosMedias.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B789CFF-CB6B-47E6-BACF-6FE821F3EE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8A10EA-9044-4651-9E2A-B93C7243B6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja2" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja3" sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja4" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="816">
   <si>
     <t>ID</t>
   </si>
@@ -2502,6 +2504,9 @@
   </si>
   <si>
     <t>Stdev % errores</t>
+  </si>
+  <si>
+    <t>Media error parada tiempo excedido</t>
   </si>
 </sst>
 </file>
@@ -2528,15 +2533,33 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2557,17 +2580,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -62189,21 +62249,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF105401-1687-48BB-8D23-B78C34DA1D47}">
   <dimension ref="A1:AM47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:39" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>805</v>
       </c>
     </row>
@@ -68939,6 +69004,9090 @@
       <c r="AM47" cm="1">
         <f t="array" ref="AM47">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A47)*(dataIntentos[Intento]=B47)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BACE07-0EAF-4DDA-9447-F7B80B3EE47F}">
+  <dimension ref="A1:AM33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>COUNTIFS(dataIntentos[Nivel],A2, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>225</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIFS(dataIntentos[Nivel],A2,dataIntentos[%Reglas respetadas ejecucion],100, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>138</v>
+      </c>
+      <c r="D2">
+        <f>COUNTIFS(dataIntentos[Nivel],A2,dataIntentos[Reglas planificacion cumplidas],"VERDADERO", dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>57</v>
+      </c>
+      <c r="E2">
+        <f>COUNTIFS(dataIntentos[Nivel],A2,dataIntentos[Completado],"VERDADERO", dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>COUNTIFS(dataIntentos[Nivel],A3, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>135</v>
+      </c>
+      <c r="C3">
+        <f>COUNTIFS(dataIntentos[Nivel],A3,dataIntentos[%Reglas respetadas ejecucion],100, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>75</v>
+      </c>
+      <c r="D3">
+        <f>COUNTIFS(dataIntentos[Nivel],A3,dataIntentos[Reglas planificacion cumplidas],"VERDADERO", dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>46</v>
+      </c>
+      <c r="E3">
+        <f>COUNTIFS(dataIntentos[Nivel],A3,dataIntentos[Completado],"VERDADERO", dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>COUNTIFS(dataIntentos[Nivel],A4, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>96</v>
+      </c>
+      <c r="C4">
+        <f>COUNTIFS(dataIntentos[Nivel],A4,dataIntentos[%Reglas respetadas ejecucion],100, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <f>COUNTIFS(dataIntentos[Nivel],A4,dataIntentos[Reglas planificacion cumplidas],"VERDADERO", dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>57</v>
+      </c>
+      <c r="E4">
+        <f>COUNTIFS(dataIntentos[Nivel],A4,dataIntentos[Completado],"VERDADERO", dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="AD5" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="AF5" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="AH5" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="AI5" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="AJ5" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="AK5" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="AL5" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="AM5" s="7" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <f>COUNTIFS(dataIntentos[Nivel],A6,dataIntentos[Intento],B6, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>41</v>
+      </c>
+      <c r="D6">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A6,dataIntentos[Intento],B6, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1463414634146343</v>
+      </c>
+      <c r="E6" cm="1">
+        <f t="array" ref="E6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.6462962956767029</v>
+      </c>
+      <c r="F6">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5853658536585367</v>
+      </c>
+      <c r="G6" cm="1">
+        <f t="array" ref="G6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3964346544682573</v>
+      </c>
+      <c r="H6">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.56097560975609762</v>
+      </c>
+      <c r="I6" cm="1">
+        <f t="array" ref="I6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.0370873963643561</v>
+      </c>
+      <c r="J6">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7073170731707317</v>
+      </c>
+      <c r="K6" cm="1">
+        <f t="array" ref="K6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>1.1737765283430208</v>
+      </c>
+      <c r="L6">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5365853658536586</v>
+      </c>
+      <c r="M6" cm="1">
+        <f t="array" ref="M6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.70182900341161747</v>
+      </c>
+      <c r="N6">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.17073170731707318</v>
+      </c>
+      <c r="O6" cm="1">
+        <f t="array" ref="O6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.79333931547758996</v>
+      </c>
+      <c r="P6">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4390243902439024</v>
+      </c>
+      <c r="Q6" cm="1">
+        <f t="array" ref="Q6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0132964916019995</v>
+      </c>
+      <c r="R6">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.0487804878048781</v>
+      </c>
+      <c r="S6" cm="1">
+        <f t="array" ref="S6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.1251280580166629</v>
+      </c>
+      <c r="T6">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="U6" cm="1">
+        <f t="array" ref="U6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.53547557073414997</v>
+      </c>
+      <c r="V6">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="W6" cm="1">
+        <f t="array" ref="W6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2097167578182677</v>
+      </c>
+      <c r="X6">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3170731707317072</v>
+      </c>
+      <c r="Y6" cm="1">
+        <f t="array" ref="Y6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1778240456243547</v>
+      </c>
+      <c r="Z6">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="AA6" cm="1">
+        <f t="array" ref="AA6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.36989636312446589</v>
+      </c>
+      <c r="AB6">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="AC6" cm="1">
+        <f t="array" ref="AC6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.36989636312446589</v>
+      </c>
+      <c r="AD6">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>206.90258536585364</v>
+      </c>
+      <c r="AE6" cm="1">
+        <f t="array" ref="AE6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>70.627255894720534</v>
+      </c>
+      <c r="AF6">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.195121951219505</v>
+      </c>
+      <c r="AG6" cm="1">
+        <f t="array" ref="AG6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>16.676578452655296</v>
+      </c>
+      <c r="AH6">
+        <f>COUNTIFS(dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>13</v>
+      </c>
+      <c r="AI6">
+        <f>COUNTIFS(dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AJ6">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>83.780487804878035</v>
+      </c>
+      <c r="AK6" cm="1">
+        <f t="array" ref="AK6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>23.379815461969745</v>
+      </c>
+      <c r="AL6">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>16.219512195121943</v>
+      </c>
+      <c r="AM6" cm="1">
+        <f t="array" ref="AM6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>23.379815461969731</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <f>COUNTIFS(dataIntentos[Nivel],A7,dataIntentos[Intento],B7, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A7,dataIntentos[Intento],B7, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.35</v>
+      </c>
+      <c r="E7" cm="1">
+        <f t="array" ref="E7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>2.5937424698685874</v>
+      </c>
+      <c r="F7">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.65</v>
+      </c>
+      <c r="G7" cm="1">
+        <f t="array" ref="G7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.7542804792848834</v>
+      </c>
+      <c r="H7">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.7</v>
+      </c>
+      <c r="I7" cm="1">
+        <f t="array" ref="I7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.4</v>
+      </c>
+      <c r="J7">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.55</v>
+      </c>
+      <c r="K7" cm="1">
+        <f t="array" ref="K7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.86458082328952912</v>
+      </c>
+      <c r="L7">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.425</v>
+      </c>
+      <c r="M7" cm="1">
+        <f t="array" ref="M7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.77095719725546374</v>
+      </c>
+      <c r="N7">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.125</v>
+      </c>
+      <c r="O7" cm="1">
+        <f t="array" ref="O7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.39921798556678278</v>
+      </c>
+      <c r="P7">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8</v>
+      </c>
+      <c r="Q7" cm="1">
+        <f t="array" ref="Q7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.0396078054371141</v>
+      </c>
+      <c r="R7">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="S7" cm="1">
+        <f t="array" ref="S7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.2939764294607534</v>
+      </c>
+      <c r="T7">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="U7" cm="1">
+        <f t="array" ref="U7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.1594718625305229</v>
+      </c>
+      <c r="V7">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="W7" cm="1">
+        <f t="array" ref="W7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.1508149286483904</v>
+      </c>
+      <c r="X7">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="Y7" cm="1">
+        <f t="array" ref="Y7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.182951816432098</v>
+      </c>
+      <c r="Z7">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AA7" cm="1">
+        <f t="array" ref="AA7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.15612494995995996</v>
+      </c>
+      <c r="AB7">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AC7" cm="1">
+        <f t="array" ref="AC7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.15612494995995996</v>
+      </c>
+      <c r="AD7">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>192.69332500000002</v>
+      </c>
+      <c r="AE7" cm="1">
+        <f t="array" ref="AE7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>97.131850561334261</v>
+      </c>
+      <c r="AF7">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>88.75</v>
+      </c>
+      <c r="AG7" cm="1">
+        <f t="array" ref="AG7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>15.761900266148114</v>
+      </c>
+      <c r="AH7">
+        <f>COUNTIFS(dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>15</v>
+      </c>
+      <c r="AI7">
+        <f>COUNTIFS(dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="AJ7">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>79.947916666666657</v>
+      </c>
+      <c r="AK7" cm="1">
+        <f t="array" ref="AK7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>31.976579360590911</v>
+      </c>
+      <c r="AL7">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>20.052083333333325</v>
+      </c>
+      <c r="AM7" cm="1">
+        <f t="array" ref="AM7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>31.976579360590883</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <f>COUNTIFS(dataIntentos[Nivel],A8,dataIntentos[Intento],B8, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>38</v>
+      </c>
+      <c r="D8">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A8,dataIntentos[Intento],B8, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6315789473684212</v>
+      </c>
+      <c r="E8" cm="1">
+        <f t="array" ref="E8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.2859780760916437</v>
+      </c>
+      <c r="F8">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1842105263157894</v>
+      </c>
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3927493286736043</v>
+      </c>
+      <c r="H8">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="I8" cm="1">
+        <f t="array" ref="I8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.6765768490622337</v>
+      </c>
+      <c r="J8">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2894736842105263</v>
+      </c>
+      <c r="K8" cm="1">
+        <f t="array" ref="K8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.60297048617839999</v>
+      </c>
+      <c r="L8">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.236842105263158</v>
+      </c>
+      <c r="M8" cm="1">
+        <f t="array" ref="M8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.62551917494761644</v>
+      </c>
+      <c r="N8">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O8" cm="1">
+        <f t="array" ref="O8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.22329687826943606</v>
+      </c>
+      <c r="P8">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3421052631578947</v>
+      </c>
+      <c r="Q8" cm="1">
+        <f t="array" ref="Q8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0072452215265599</v>
+      </c>
+      <c r="R8">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="S8" cm="1">
+        <f t="array" ref="S8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.0989796325169001</v>
+      </c>
+      <c r="T8">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.39473684210526316</v>
+      </c>
+      <c r="U8" cm="1">
+        <f t="array" ref="U8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.67040732646615775</v>
+      </c>
+      <c r="V8">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7105263157894739</v>
+      </c>
+      <c r="W8" cm="1">
+        <f t="array" ref="W8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0980340023697404</v>
+      </c>
+      <c r="X8">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1052631578947367</v>
+      </c>
+      <c r="Y8" cm="1">
+        <f t="array" ref="Y8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.2729880655208237</v>
+      </c>
+      <c r="Z8">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="AA8" cm="1">
+        <f t="array" ref="AA8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.16007269816574263</v>
+      </c>
+      <c r="AB8">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="AC8" cm="1">
+        <f t="array" ref="AC8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.16007269816574263</v>
+      </c>
+      <c r="AD8">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>174.7833157894737</v>
+      </c>
+      <c r="AE8" cm="1">
+        <f t="array" ref="AE8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>53.737721293776936</v>
+      </c>
+      <c r="AF8">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>90.131578947368425</v>
+      </c>
+      <c r="AG8" cm="1">
+        <f t="array" ref="AG8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>13.498871400449469</v>
+      </c>
+      <c r="AH8">
+        <f>COUNTIFS(dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7</v>
+      </c>
+      <c r="AI8">
+        <f>COUNTIFS(dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AJ8">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.578947368421041</v>
+      </c>
+      <c r="AK8" cm="1">
+        <f t="array" ref="AK8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>26.501537438633012</v>
+      </c>
+      <c r="AL8">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.421052631578945</v>
+      </c>
+      <c r="AM8" cm="1">
+        <f t="array" ref="AM8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>26.501537438632973</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <f>COUNTIFS(dataIntentos[Nivel],A9,dataIntentos[Intento],B9, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>28</v>
+      </c>
+      <c r="D9">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A9,dataIntentos[Intento],B9, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="E9" cm="1">
+        <f t="array" ref="E9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.6174274106034645</v>
+      </c>
+      <c r="F9">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="G9" cm="1">
+        <f t="array" ref="G9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.4880476182856899</v>
+      </c>
+      <c r="H9">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.75</v>
+      </c>
+      <c r="I9" cm="1">
+        <f t="array" ref="I9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.91123934444093391</v>
+      </c>
+      <c r="J9">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2857142857142858</v>
+      </c>
+      <c r="K9" cm="1">
+        <f t="array" ref="K9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.88063057185271088</v>
+      </c>
+      <c r="L9">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.1785714285714286</v>
+      </c>
+      <c r="M9" cm="1">
+        <f t="array" ref="M9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.88856109318748067</v>
+      </c>
+      <c r="N9">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="O9" cm="1">
+        <f t="array" ref="O9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.30929478706587094</v>
+      </c>
+      <c r="P9">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4642857142857142</v>
+      </c>
+      <c r="Q9" cm="1">
+        <f t="array" ref="Q9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.2095495872768642</v>
+      </c>
+      <c r="R9">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="S9" cm="1">
+        <f t="array" ref="S9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.0708331678974965</v>
+      </c>
+      <c r="T9">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="U9" cm="1">
+        <f t="array" ref="U9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.89499743472440485</v>
+      </c>
+      <c r="V9">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="W9" cm="1">
+        <f t="array" ref="W9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.265717510476382</v>
+      </c>
+      <c r="X9">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8214285714285714</v>
+      </c>
+      <c r="Y9" cm="1">
+        <f t="array" ref="Y9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.2832317302301202</v>
+      </c>
+      <c r="Z9">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" cm="1">
+        <f t="array" ref="AA9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC9" cm="1">
+        <f t="array" ref="AC9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>182.15225000000001</v>
+      </c>
+      <c r="AE9" cm="1">
+        <f t="array" ref="AE9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>91.531177182432202</v>
+      </c>
+      <c r="AF9">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.714285714285708</v>
+      </c>
+      <c r="AG9" cm="1">
+        <f t="array" ref="AG9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>14.060728346449663</v>
+      </c>
+      <c r="AH9">
+        <f>COUNTIFS(dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AI9">
+        <f>COUNTIFS(dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>72.193877551020393</v>
+      </c>
+      <c r="AK9" cm="1">
+        <f t="array" ref="AK9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>32.276828208862113</v>
+      </c>
+      <c r="AL9">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>27.806122448979583</v>
+      </c>
+      <c r="AM9" cm="1">
+        <f t="array" ref="AM9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>32.276828208862106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <f>COUNTIFS(dataIntentos[Nivel],A10,dataIntentos[Intento],B10, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A10,dataIntentos[Intento],B10, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7692307692307692</v>
+      </c>
+      <c r="E10" cm="1">
+        <f t="array" ref="E10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.2802551520840952</v>
+      </c>
+      <c r="F10">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2307692307692308</v>
+      </c>
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.2498520622516862</v>
+      </c>
+      <c r="H10">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="I10" cm="1">
+        <f t="array" ref="I10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.0462669622104188</v>
+      </c>
+      <c r="J10">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3461538461538463</v>
+      </c>
+      <c r="K10" cm="1">
+        <f t="array" ref="K10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.61658536699543831</v>
+      </c>
+      <c r="L10">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3076923076923077</v>
+      </c>
+      <c r="M10" cm="1">
+        <f t="array" ref="M10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.66617338752649125</v>
+      </c>
+      <c r="N10">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="O10" cm="1">
+        <f t="array" ref="O10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="P10">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4230769230769231</v>
+      </c>
+      <c r="Q10" cm="1">
+        <f t="array" ref="Q10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0803516850144723</v>
+      </c>
+      <c r="R10">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="S10" cm="1">
+        <f t="array" ref="S10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.87367820704619592</v>
+      </c>
+      <c r="T10">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="U10" cm="1">
+        <f t="array" ref="U10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.0469736606781692</v>
+      </c>
+      <c r="V10">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3846153846153846</v>
+      </c>
+      <c r="W10" cm="1">
+        <f t="array" ref="W10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2113858267710478</v>
+      </c>
+      <c r="X10">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7307692307692308</v>
+      </c>
+      <c r="Y10" cm="1">
+        <f t="array" ref="Y10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1285692885477854</v>
+      </c>
+      <c r="Z10">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" cm="1">
+        <f t="array" ref="AA10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC10" cm="1">
+        <f t="array" ref="AC10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>183.06</v>
+      </c>
+      <c r="AE10" cm="1">
+        <f t="array" ref="AE10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>87.715579105249148</v>
+      </c>
+      <c r="AF10">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>91.34615384615384</v>
+      </c>
+      <c r="AG10" cm="1">
+        <f t="array" ref="AG10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.893573920050944</v>
+      </c>
+      <c r="AH10">
+        <f>COUNTIFS(dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6</v>
+      </c>
+      <c r="AI10">
+        <f>COUNTIFS(dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ10">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.089743589743577</v>
+      </c>
+      <c r="AK10" cm="1">
+        <f t="array" ref="AK10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>31.398807437246159</v>
+      </c>
+      <c r="AL10">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.910256410256409</v>
+      </c>
+      <c r="AM10" cm="1">
+        <f t="array" ref="AM10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>31.39880743724612</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <f>COUNTIFS(dataIntentos[Nivel],A11,dataIntentos[Intento],B11, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A11,dataIntentos[Intento],B11, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.6111111111111112</v>
+      </c>
+      <c r="E11" cm="1">
+        <f t="array" ref="E11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.37997137204158</v>
+      </c>
+      <c r="F11">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="G11" cm="1">
+        <f t="array" ref="G11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.4098419489388356</v>
+      </c>
+      <c r="H11">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="I11" cm="1">
+        <f t="array" ref="I11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="J11">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6111111111111112</v>
+      </c>
+      <c r="K11" cm="1">
+        <f t="array" ref="K11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.48749802152178456</v>
+      </c>
+      <c r="L11">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="M11" cm="1">
+        <f t="array" ref="M11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.49690399499995325</v>
+      </c>
+      <c r="N11">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="O11" cm="1">
+        <f t="array" ref="O11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.22906142364542559</v>
+      </c>
+      <c r="P11">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q11" cm="1">
+        <f t="array" ref="Q11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="R11">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="S11" cm="1">
+        <f t="array" ref="S11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.11665284679121</v>
+      </c>
+      <c r="T11">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="U11" cm="1">
+        <f t="array" ref="U11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.1653431646335017</v>
+      </c>
+      <c r="V11">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7222222222222223</v>
+      </c>
+      <c r="W11" cm="1">
+        <f t="array" ref="W11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0957268290731121</v>
+      </c>
+      <c r="X11">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y11" cm="1">
+        <f t="array" ref="Y11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0540925533894598</v>
+      </c>
+      <c r="Z11">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" cm="1">
+        <f t="array" ref="AA11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" cm="1">
+        <f t="array" ref="AC11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>178.98477777777782</v>
+      </c>
+      <c r="AE11" cm="1">
+        <f t="array" ref="AE11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>57.451810645053229</v>
+      </c>
+      <c r="AF11">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.055555555555557</v>
+      </c>
+      <c r="AG11" cm="1">
+        <f t="array" ref="AG11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.197580205970208</v>
+      </c>
+      <c r="AH11">
+        <f>COUNTIFS(dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI11">
+        <f>COUNTIFS(dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ11">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>88.425925925925924</v>
+      </c>
+      <c r="AK11" cm="1">
+        <f t="array" ref="AK11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>22.246321808766616</v>
+      </c>
+      <c r="AL11">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>11.574074074074073</v>
+      </c>
+      <c r="AM11" cm="1">
+        <f t="array" ref="AM11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>22.246321808766591</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(dataIntentos[Nivel],A12,dataIntentos[Intento],B12, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A12,dataIntentos[Intento],B12, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="E12" cm="1">
+        <f t="array" ref="E12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>2.411706145162019</v>
+      </c>
+      <c r="F12">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.6659862556700857</v>
+      </c>
+      <c r="H12">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I12" cm="1">
+        <f t="array" ref="I12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.1866605518454392</v>
+      </c>
+      <c r="J12">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.49487165930539351</v>
+      </c>
+      <c r="L12">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M12" cm="1">
+        <f t="array" ref="M12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.62678317052800869</v>
+      </c>
+      <c r="N12">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="O12" cm="1">
+        <f t="array" ref="O12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.25753937681885641</v>
+      </c>
+      <c r="P12">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q12" cm="1">
+        <f t="array" ref="Q12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.2677868380553634</v>
+      </c>
+      <c r="R12">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2142857142857142</v>
+      </c>
+      <c r="S12" cm="1">
+        <f t="array" ref="S12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.5202711895566259</v>
+      </c>
+      <c r="T12">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="U12" cm="1">
+        <f t="array" ref="U12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.2058530725810095</v>
+      </c>
+      <c r="V12">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="W12" cm="1">
+        <f t="array" ref="W12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2371791482634837</v>
+      </c>
+      <c r="X12">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y12" cm="1">
+        <f t="array" ref="Y12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1952286093343936</v>
+      </c>
+      <c r="Z12">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA12" cm="1">
+        <f t="array" ref="AA12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC12" cm="1">
+        <f t="array" ref="AC12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>197.20271428571431</v>
+      </c>
+      <c r="AE12" cm="1">
+        <f t="array" ref="AE12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>96.956797791909437</v>
+      </c>
+      <c r="AF12">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG12" cm="1">
+        <f t="array" ref="AG12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
+        <f>COUNTIFS(dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AI12">
+        <f>COUNTIFS(dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>77.414965986394549</v>
+      </c>
+      <c r="AK12" cm="1">
+        <f t="array" ref="AK12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>27.697352218452188</v>
+      </c>
+      <c r="AL12">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>22.58503401360543</v>
+      </c>
+      <c r="AM12" cm="1">
+        <f t="array" ref="AM12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>27.697352218452195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(dataIntentos[Nivel],A13,dataIntentos[Intento],B13, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A13,dataIntentos[Intento],B13, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.2222222222222223</v>
+      </c>
+      <c r="E13" cm="1">
+        <f t="array" ref="E13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.3146843962443591</v>
+      </c>
+      <c r="F13">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="H13">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="I13" cm="1">
+        <f t="array" ref="I13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.41573970964154905</v>
+      </c>
+      <c r="J13">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="K13" cm="1">
+        <f t="array" ref="K13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.6849348892187751</v>
+      </c>
+      <c r="L13">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="M13" cm="1">
+        <f t="array" ref="M13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.6849348892187751</v>
+      </c>
+      <c r="N13">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O13" cm="1">
+        <f t="array" ref="O13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Q13" cm="1">
+        <f t="array" ref="Q13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="R13">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4444444444444444</v>
+      </c>
+      <c r="S13" cm="1">
+        <f t="array" ref="S13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.4229164972072998</v>
+      </c>
+      <c r="T13">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U13" cm="1">
+        <f t="array" ref="U13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.41573970964154905</v>
+      </c>
+      <c r="V13">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="W13" cm="1">
+        <f t="array" ref="W13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0999438818457405</v>
+      </c>
+      <c r="X13">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="Y13" cm="1">
+        <f t="array" ref="Y13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0540925533894598</v>
+      </c>
+      <c r="Z13">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA13" cm="1">
+        <f t="array" ref="AA13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" cm="1">
+        <f t="array" ref="AC13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>185.7378888888889</v>
+      </c>
+      <c r="AE13" cm="1">
+        <f t="array" ref="AE13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>52.788105329903466</v>
+      </c>
+      <c r="AF13">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>94.444444444444443</v>
+      </c>
+      <c r="AG13" cm="1">
+        <f t="array" ref="AG13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>10.393492741038726</v>
+      </c>
+      <c r="AH13">
+        <f>COUNTIFS(dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <f>COUNTIFS(dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>91.666666666666671</v>
+      </c>
+      <c r="AK13" cm="1">
+        <f t="array" ref="AK13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="AL13">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="AM13" cm="1">
+        <f t="array" ref="AM13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>16.666666666666668</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <f>COUNTIFS(dataIntentos[Nivel],A14,dataIntentos[Intento],B14, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A14,dataIntentos[Intento],B14, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="E14" cm="1">
+        <f t="array" ref="E14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.1989578808281798</v>
+      </c>
+      <c r="F14">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.125</v>
+      </c>
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3635890143294642</v>
+      </c>
+      <c r="H14">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.125</v>
+      </c>
+      <c r="I14" cm="1">
+        <f t="array" ref="I14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.33071891388307384</v>
+      </c>
+      <c r="J14">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.625</v>
+      </c>
+      <c r="K14" cm="1">
+        <f t="array" ref="K14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.48412291827592713</v>
+      </c>
+      <c r="L14">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.625</v>
+      </c>
+      <c r="M14" cm="1">
+        <f t="array" ref="M14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.48412291827592713</v>
+      </c>
+      <c r="N14">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O14" cm="1">
+        <f t="array" ref="O14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.625</v>
+      </c>
+      <c r="Q14" cm="1">
+        <f t="array" ref="Q14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.85695682505013049</v>
+      </c>
+      <c r="R14">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S14" cm="1">
+        <f t="array" ref="S14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.125</v>
+      </c>
+      <c r="U14" cm="1">
+        <f t="array" ref="U14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.33071891388307384</v>
+      </c>
+      <c r="V14">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.125</v>
+      </c>
+      <c r="W14" cm="1">
+        <f t="array" ref="W14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.78062474979979979</v>
+      </c>
+      <c r="X14">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="Y14" cm="1">
+        <f t="array" ref="Y14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1989578808281798</v>
+      </c>
+      <c r="Z14">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA14" cm="1">
+        <f t="array" ref="AA14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC14" cm="1">
+        <f t="array" ref="AC14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>176.21562500000002</v>
+      </c>
+      <c r="AE14" cm="1">
+        <f t="array" ref="AE14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>58.38293383116654</v>
+      </c>
+      <c r="AF14">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>96.875</v>
+      </c>
+      <c r="AG14" cm="1">
+        <f t="array" ref="AG14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>8.2679728470768463</v>
+      </c>
+      <c r="AH14">
+        <f>COUNTIFS(dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI14">
+        <f>COUNTIFS(dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.75</v>
+      </c>
+      <c r="AK14" cm="1">
+        <f t="array" ref="AK14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>16.535945694153693</v>
+      </c>
+      <c r="AL14">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6.25</v>
+      </c>
+      <c r="AM14" cm="1">
+        <f t="array" ref="AM14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>16.535945694153693</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
+        <f>COUNTIFS(dataIntentos[Nivel],A15,dataIntentos[Intento],B15, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A15,dataIntentos[Intento],B15, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="E15" cm="1">
+        <f t="array" ref="E15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.6329931618554521</v>
+      </c>
+      <c r="F15">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="G15" cm="1">
+        <f t="array" ref="G15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.0548046676563256</v>
+      </c>
+      <c r="H15">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I15" cm="1">
+        <f t="array" ref="I15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="J15">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="K15" cm="1">
+        <f t="array" ref="K15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="L15">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="M15" cm="1">
+        <f t="array" ref="M15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="N15">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O15" cm="1">
+        <f t="array" ref="O15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="P15">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Q15" cm="1">
+        <f t="array" ref="Q15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="R15">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="S15" cm="1">
+        <f t="array" ref="S15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="T15">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U15" cm="1">
+        <f t="array" ref="U15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="V15">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="W15" cm="1">
+        <f t="array" ref="W15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.8856180831641267</v>
+      </c>
+      <c r="X15">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Y15" cm="1">
+        <f t="array" ref="Y15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="Z15">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AA15" cm="1">
+        <f t="array" ref="AA15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="AB15">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AC15" cm="1">
+        <f t="array" ref="AC15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="AD15">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>161.75333333333333</v>
+      </c>
+      <c r="AE15" cm="1">
+        <f t="array" ref="AE15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>38.489508582065433</v>
+      </c>
+      <c r="AF15">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>75</v>
+      </c>
+      <c r="AG15" cm="1">
+        <f t="array" ref="AG15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>20.412414523193153</v>
+      </c>
+      <c r="AH15">
+        <f>COUNTIFS(dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <f>COUNTIFS(dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>55.555555555555536</v>
+      </c>
+      <c r="AK15" cm="1">
+        <f t="array" ref="AK15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>41.573970964154888</v>
+      </c>
+      <c r="AL15">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>44.444444444444436</v>
+      </c>
+      <c r="AM15" cm="1">
+        <f t="array" ref="AM15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>41.573970964154903</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <f>COUNTIFS(dataIntentos[Nivel],A16,dataIntentos[Intento],B16, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>49</v>
+      </c>
+      <c r="D16">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A16,dataIntentos[Intento],B16, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.2448979591836733</v>
+      </c>
+      <c r="E16" cm="1">
+        <f t="array" ref="E16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.4642768256858856</v>
+      </c>
+      <c r="F16">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7551020408163267</v>
+      </c>
+      <c r="G16" cm="1">
+        <f t="array" ref="G16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.597582513533137</v>
+      </c>
+      <c r="H16">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.48979591836734693</v>
+      </c>
+      <c r="I16" cm="1">
+        <f t="array" ref="I16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.83598772033730784</v>
+      </c>
+      <c r="J16">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7755102040816326</v>
+      </c>
+      <c r="K16" cm="1">
+        <f t="array" ref="K16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.86343656331861951</v>
+      </c>
+      <c r="L16">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6326530612244898</v>
+      </c>
+      <c r="M16" cm="1">
+        <f t="array" ref="M16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.91904736728144509</v>
+      </c>
+      <c r="N16">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O16" cm="1">
+        <f t="array" ref="O16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.40406101782088427</v>
+      </c>
+      <c r="P16">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4693877551020409</v>
+      </c>
+      <c r="Q16" cm="1">
+        <f t="array" ref="Q16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0321770299103503</v>
+      </c>
+      <c r="R16">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.1224489795918366</v>
+      </c>
+      <c r="S16" cm="1">
+        <f t="array" ref="S16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.0997709049230595</v>
+      </c>
+      <c r="T16">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.34693877551020408</v>
+      </c>
+      <c r="U16" cm="1">
+        <f t="array" ref="U16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.59078019698490325</v>
+      </c>
+      <c r="V16">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3673469387755102</v>
+      </c>
+      <c r="W16" cm="1">
+        <f t="array" ref="W16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.84982297198600054</v>
+      </c>
+      <c r="X16">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="Y16" cm="1">
+        <f t="array" ref="Y16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="Z16">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.44897959183673469</v>
+      </c>
+      <c r="AA16" cm="1">
+        <f t="array" ref="AA16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.70163728317024832</v>
+      </c>
+      <c r="AB16">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AC16" cm="1">
+        <f t="array" ref="AC16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.88063057185271088</v>
+      </c>
+      <c r="AD16">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>256.78400000000005</v>
+      </c>
+      <c r="AE16" cm="1">
+        <f t="array" ref="AE16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>114.92059284691187</v>
+      </c>
+      <c r="AF16">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.122448979591837</v>
+      </c>
+      <c r="AG16" cm="1">
+        <f t="array" ref="AG16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>20.535318160712354</v>
+      </c>
+      <c r="AH16">
+        <f>COUNTIFS(dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>22</v>
+      </c>
+      <c r="AI16">
+        <f>COUNTIFS(dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="AJ16">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.103012633624886</v>
+      </c>
+      <c r="AK16" cm="1">
+        <f t="array" ref="AK16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>31.355699814623836</v>
+      </c>
+      <c r="AL16">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.896987366375111</v>
+      </c>
+      <c r="AM16" cm="1">
+        <f t="array" ref="AM16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>31.355699814623875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <f>COUNTIFS(dataIntentos[Nivel],A17,dataIntentos[Intento],B17, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A17,dataIntentos[Intento],B17, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5384615384615383</v>
+      </c>
+      <c r="E17" cm="1">
+        <f t="array" ref="E17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.0462669622104188</v>
+      </c>
+      <c r="F17">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3076923076923075</v>
+      </c>
+      <c r="G17" cm="1">
+        <f t="array" ref="G17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.1013708510212579</v>
+      </c>
+      <c r="H17">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="I17" cm="1">
+        <f t="array" ref="I17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.42132504423474315</v>
+      </c>
+      <c r="J17">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8461538461538463</v>
+      </c>
+      <c r="K17" cm="1">
+        <f t="array" ref="K17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.45508306023843198</v>
+      </c>
+      <c r="L17">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8076923076923077</v>
+      </c>
+      <c r="M17" cm="1">
+        <f t="array" ref="M17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.48192169562083337</v>
+      </c>
+      <c r="N17">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="O17" cm="1">
+        <f t="array" ref="O17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="P17">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6923076923076923</v>
+      </c>
+      <c r="Q17" cm="1">
+        <f t="array" ref="Q17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.82131371169471623</v>
+      </c>
+      <c r="R17">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S17" cm="1">
+        <f t="array" ref="S17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.88795356773963041</v>
+      </c>
+      <c r="T17">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="U17" cm="1">
+        <f t="array" ref="U17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.39411349099844606</v>
+      </c>
+      <c r="V17">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.7307692307692308</v>
+      </c>
+      <c r="W17" cm="1">
+        <f t="array" ref="W17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.44356009979503064</v>
+      </c>
+      <c r="X17">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3846153846153846</v>
+      </c>
+      <c r="Y17" cm="1">
+        <f t="array" ref="Y17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1461280327501031</v>
+      </c>
+      <c r="Z17">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AA17" cm="1">
+        <f t="array" ref="AA17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.57563959796522179</v>
+      </c>
+      <c r="AB17">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="AC17" cm="1">
+        <f t="array" ref="AC17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.71023789663920722</v>
+      </c>
+      <c r="AD17">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>353.86403846153854</v>
+      </c>
+      <c r="AE17" cm="1">
+        <f t="array" ref="AE17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>566.12742751905648</v>
+      </c>
+      <c r="AF17">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>90.384615384615387</v>
+      </c>
+      <c r="AG17" cm="1">
+        <f t="array" ref="AG17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>14.000211325539457</v>
+      </c>
+      <c r="AH17">
+        <f>COUNTIFS(dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>16</v>
+      </c>
+      <c r="AI17">
+        <f>COUNTIFS(dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>11</v>
+      </c>
+      <c r="AJ17">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.012820512820497</v>
+      </c>
+      <c r="AK17" cm="1">
+        <f t="array" ref="AK17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>13.697114540864565</v>
+      </c>
+      <c r="AL17">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6.9871794871794846</v>
+      </c>
+      <c r="AM17" cm="1">
+        <f t="array" ref="AM17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>13.697114540864508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <f>COUNTIFS(dataIntentos[Nivel],A18,dataIntentos[Intento],B18, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A18,dataIntentos[Intento],B18, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="E18" cm="1">
+        <f t="array" ref="E18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.2133516482134197</v>
+      </c>
+      <c r="F18">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5833333333333335</v>
+      </c>
+      <c r="G18" cm="1">
+        <f t="array" ref="G18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3202482931462383</v>
+      </c>
+      <c r="H18">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.25</v>
+      </c>
+      <c r="I18" cm="1">
+        <f t="array" ref="I18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="J18">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5833333333333333</v>
+      </c>
+      <c r="K18" cm="1">
+        <f t="array" ref="K18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.75920279826202486</v>
+      </c>
+      <c r="L18">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M18" cm="1">
+        <f t="array" ref="M18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.76376261582597338</v>
+      </c>
+      <c r="N18">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="O18" cm="1">
+        <f t="array" ref="O18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.27638539919628335</v>
+      </c>
+      <c r="P18">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q18" cm="1">
+        <f t="array" ref="Q18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.59511903571190417</v>
+      </c>
+      <c r="R18">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.0833333333333333</v>
+      </c>
+      <c r="S18" cm="1">
+        <f t="array" ref="S18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.75920279826202486</v>
+      </c>
+      <c r="T18">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U18" cm="1">
+        <f t="array" ref="U18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.37267799624996495</v>
+      </c>
+      <c r="V18">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="W18" cm="1">
+        <f t="array" ref="W18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.1426091000668408</v>
+      </c>
+      <c r="X18">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Y18" cm="1">
+        <f t="array" ref="Y18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0274023338281628</v>
+      </c>
+      <c r="Z18">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA18" cm="1">
+        <f t="array" ref="AA18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.62360956446232352</v>
+      </c>
+      <c r="AB18">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AC18" cm="1">
+        <f t="array" ref="AC18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.62360956446232352</v>
+      </c>
+      <c r="AD18">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>221.69291666666666</v>
+      </c>
+      <c r="AE18" cm="1">
+        <f t="array" ref="AE18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>100.58739560489862</v>
+      </c>
+      <c r="AF18">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG18" cm="1">
+        <f t="array" ref="AG18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH18">
+        <f>COUNTIFS(dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI18">
+        <f>COUNTIFS(dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>86.805555555555543</v>
+      </c>
+      <c r="AK18" cm="1">
+        <f t="array" ref="AK18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>28.353410642491156</v>
+      </c>
+      <c r="AL18">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>13.194444444444443</v>
+      </c>
+      <c r="AM18" cm="1">
+        <f t="array" ref="AM18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>28.353410642491113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <f>COUNTIFS(dataIntentos[Nivel],A19,dataIntentos[Intento],B19, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A19,dataIntentos[Intento],B19, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.0909090909090908</v>
+      </c>
+      <c r="E19" cm="1">
+        <f t="array" ref="E19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.311109554714178</v>
+      </c>
+      <c r="F19">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6363636363636362</v>
+      </c>
+      <c r="G19" cm="1">
+        <f t="array" ref="G19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3666633071248098</v>
+      </c>
+      <c r="H19">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="I19" cm="1">
+        <f t="array" ref="I19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.655554777357089</v>
+      </c>
+      <c r="J19">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6363636363636365</v>
+      </c>
+      <c r="K19" cm="1">
+        <f t="array" ref="K19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.77138921583987008</v>
+      </c>
+      <c r="L19">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4545454545454546</v>
+      </c>
+      <c r="M19" cm="1">
+        <f t="array" ref="M19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.655554777357089</v>
+      </c>
+      <c r="N19">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="O19" cm="1">
+        <f t="array" ref="O19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.57495957457606894</v>
+      </c>
+      <c r="P19">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4545454545454546</v>
+      </c>
+      <c r="Q19" cm="1">
+        <f t="array" ref="Q19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.89072354283024657</v>
+      </c>
+      <c r="R19">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.1818181818181819</v>
+      </c>
+      <c r="S19" cm="1">
+        <f t="array" ref="S19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.93596637645336367</v>
+      </c>
+      <c r="T19">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U19" cm="1">
+        <f t="array" ref="U19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.44536177141512329</v>
+      </c>
+      <c r="V19">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1818181818181817</v>
+      </c>
+      <c r="W19" cm="1">
+        <f t="array" ref="W19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.1134044285378082</v>
+      </c>
+      <c r="X19">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8181818181818181</v>
+      </c>
+      <c r="Y19" cm="1">
+        <f t="array" ref="Y19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1922615498730911</v>
+      </c>
+      <c r="Z19">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="AA19" cm="1">
+        <f t="array" ref="AA19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.28747978728803447</v>
+      </c>
+      <c r="AB19">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AC19" cm="1">
+        <f t="array" ref="AC19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.38569460791993504</v>
+      </c>
+      <c r="AD19">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>199.15018181818184</v>
+      </c>
+      <c r="AE19" cm="1">
+        <f t="array" ref="AE19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>82.015212675141896</v>
+      </c>
+      <c r="AF19">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>88.63636363636364</v>
+      </c>
+      <c r="AG19" cm="1">
+        <f t="array" ref="AG19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.44823994329923</v>
+      </c>
+      <c r="AH19">
+        <f>COUNTIFS(dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI19">
+        <f>COUNTIFS(dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="AJ19">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.515151515151516</v>
+      </c>
+      <c r="AK19" cm="1">
+        <f t="array" ref="AK19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>30.529457090318004</v>
+      </c>
+      <c r="AL19">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.484848484848484</v>
+      </c>
+      <c r="AM19" cm="1">
+        <f t="array" ref="AM19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>30.529457090318004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <f>COUNTIFS(dataIntentos[Nivel],A20,dataIntentos[Intento],B20, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A20,dataIntentos[Intento],B20, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="E20" cm="1">
+        <f t="array" ref="E20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.68718427093627676</v>
+      </c>
+      <c r="F20">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="G20" cm="1">
+        <f t="array" ref="G20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.68718427093627676</v>
+      </c>
+      <c r="H20">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I20" cm="1">
+        <f t="array" ref="I20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="K20" cm="1">
+        <f t="array" ref="K20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="L20">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M20" cm="1">
+        <f t="array" ref="M20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="N20">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O20" cm="1">
+        <f t="array" ref="O20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Q20" cm="1">
+        <f t="array" ref="Q20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.37267799624996495</v>
+      </c>
+      <c r="R20">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="S20" cm="1">
+        <f t="array" ref="S20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.37267799624996495</v>
+      </c>
+      <c r="T20">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U20" cm="1">
+        <f t="array" ref="U20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W20" cm="1">
+        <f t="array" ref="W20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.7453559924999299</v>
+      </c>
+      <c r="X20">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y20" cm="1">
+        <f t="array" ref="Y20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA20" cm="1">
+        <f t="array" ref="AA20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="AB20">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AC20" cm="1">
+        <f t="array" ref="AC20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="AD20">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>236.47566666666668</v>
+      </c>
+      <c r="AE20" cm="1">
+        <f t="array" ref="AE20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>22.077209218759709</v>
+      </c>
+      <c r="AF20">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>91.666666666666671</v>
+      </c>
+      <c r="AG20" cm="1">
+        <f t="array" ref="AG20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.785113019775793</v>
+      </c>
+      <c r="AH20">
+        <f>COUNTIFS(dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <f>COUNTIFS(dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK20" cm="1">
+        <f t="array" ref="AK20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM20" cm="1">
+        <f t="array" ref="AM20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <f>COUNTIFS(dataIntentos[Nivel],A21,dataIntentos[Intento],B21, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A21,dataIntentos[Intento],B21, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="E21" cm="1">
+        <f t="array" ref="E21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="F21">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="G21" cm="1">
+        <f t="array" ref="G21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="H21">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I21" cm="1">
+        <f t="array" ref="I21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="K21" cm="1">
+        <f t="array" ref="K21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="L21">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M21" cm="1">
+        <f t="array" ref="M21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="N21">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O21" cm="1">
+        <f t="array" ref="O21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q21" cm="1">
+        <f t="array" ref="Q21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="R21">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="S21" cm="1">
+        <f t="array" ref="S21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="T21">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U21" cm="1">
+        <f t="array" ref="U21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="W21" cm="1">
+        <f t="array" ref="W21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="X21">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5</v>
+      </c>
+      <c r="Y21" cm="1">
+        <f t="array" ref="Y21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1180339887498949</v>
+      </c>
+      <c r="Z21">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" cm="1">
+        <f t="array" ref="AA21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC21" cm="1">
+        <f t="array" ref="AC21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>209.43324999999999</v>
+      </c>
+      <c r="AE21" cm="1">
+        <f t="array" ref="AE21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>74.057046141386877</v>
+      </c>
+      <c r="AF21">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AG21" cm="1">
+        <f t="array" ref="AG21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <f>COUNTIFS(dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <f>COUNTIFS(dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK21" cm="1">
+        <f t="array" ref="AK21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM21" cm="1">
+        <f t="array" ref="AM21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <f>COUNTIFS(dataIntentos[Nivel],A22,dataIntentos[Intento],B22, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A22,dataIntentos[Intento],B22, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="E22" cm="1">
+        <f t="array" ref="E22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.0897247358851685</v>
+      </c>
+      <c r="F22">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="G22" cm="1">
+        <f t="array" ref="G22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.0897247358851685</v>
+      </c>
+      <c r="H22">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I22" cm="1">
+        <f t="array" ref="I22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="K22" cm="1">
+        <f t="array" ref="K22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="L22">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="M22" cm="1">
+        <f t="array" ref="M22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="N22">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O22" cm="1">
+        <f t="array" ref="O22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="Q22" cm="1">
+        <f t="array" ref="Q22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="R22">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="S22" cm="1">
+        <f t="array" ref="S22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="T22">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U22" cm="1">
+        <f t="array" ref="U22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="W22" cm="1">
+        <f t="array" ref="W22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="X22">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5</v>
+      </c>
+      <c r="Y22" cm="1">
+        <f t="array" ref="Y22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1180339887498949</v>
+      </c>
+      <c r="Z22">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA22" cm="1">
+        <f t="array" ref="AA22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC22" cm="1">
+        <f t="array" ref="AC22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>182.77575000000002</v>
+      </c>
+      <c r="AE22" cm="1">
+        <f t="array" ref="AE22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>102.49415469034074</v>
+      </c>
+      <c r="AF22">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AG22" cm="1">
+        <f t="array" ref="AG22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <f>COUNTIFS(dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <f>COUNTIFS(dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK22" cm="1">
+        <f t="array" ref="AK22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM22" cm="1">
+        <f t="array" ref="AM22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <f>COUNTIFS(dataIntentos[Nivel],A23,dataIntentos[Intento],B23, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A23,dataIntentos[Intento],B23, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8</v>
+      </c>
+      <c r="E23" cm="1">
+        <f t="array" ref="E23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>3.2496153618543842</v>
+      </c>
+      <c r="F23">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6</v>
+      </c>
+      <c r="G23" cm="1">
+        <f t="array" ref="G23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.1540659228538015</v>
+      </c>
+      <c r="H23">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2</v>
+      </c>
+      <c r="I23" cm="1">
+        <f t="array" ref="I23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.6</v>
+      </c>
+      <c r="J23">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.4</v>
+      </c>
+      <c r="K23" cm="1">
+        <f t="array" ref="K23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>1.8547236990991407</v>
+      </c>
+      <c r="L23">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M23" cm="1">
+        <f t="array" ref="M23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>2.0396078054371141</v>
+      </c>
+      <c r="N23">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.2</v>
+      </c>
+      <c r="O23" cm="1">
+        <f t="array" ref="O23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.4</v>
+      </c>
+      <c r="P23">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4</v>
+      </c>
+      <c r="Q23" cm="1">
+        <f t="array" ref="Q23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.4966629547095767</v>
+      </c>
+      <c r="R23">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.4</v>
+      </c>
+      <c r="S23" cm="1">
+        <f t="array" ref="S23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.8</v>
+      </c>
+      <c r="T23">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="U23" cm="1">
+        <f t="array" ref="U23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.5491933384829668</v>
+      </c>
+      <c r="V23">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="W23" cm="1">
+        <f t="array" ref="W23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2649110640673518</v>
+      </c>
+      <c r="X23">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.8</v>
+      </c>
+      <c r="Y23" cm="1">
+        <f t="array" ref="Y23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1661903789690602</v>
+      </c>
+      <c r="Z23">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" cm="1">
+        <f t="array" ref="AA23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.2</v>
+      </c>
+      <c r="AC23" cm="1">
+        <f t="array" ref="AC23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.4</v>
+      </c>
+      <c r="AD23">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>199.17119999999997</v>
+      </c>
+      <c r="AE23" cm="1">
+        <f t="array" ref="AE23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>200.19441443197161</v>
+      </c>
+      <c r="AF23">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85</v>
+      </c>
+      <c r="AG23" cm="1">
+        <f t="array" ref="AG23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>20</v>
+      </c>
+      <c r="AH23">
+        <f>COUNTIFS(dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <f>COUNTIFS(dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>72</v>
+      </c>
+      <c r="AK23" cm="1">
+        <f t="array" ref="AK23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>39.191835884530846</v>
+      </c>
+      <c r="AL23">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>28</v>
+      </c>
+      <c r="AM23" cm="1">
+        <f t="array" ref="AM23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>39.191835884530846</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <f>COUNTIFS(dataIntentos[Nivel],A24,dataIntentos[Intento],B24, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A24,dataIntentos[Intento],B24, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="E24" cm="1">
+        <f t="array" ref="E24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.0897247358851685</v>
+      </c>
+      <c r="F24">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.75</v>
+      </c>
+      <c r="G24" cm="1">
+        <f t="array" ref="G24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.299038105676658</v>
+      </c>
+      <c r="H24">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="I24" cm="1">
+        <f t="array" ref="I24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="J24">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="K24" cm="1">
+        <f t="array" ref="K24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="L24">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="M24" cm="1">
+        <f t="array" ref="M24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="N24">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O24" cm="1">
+        <f t="array" ref="O24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="Q24" cm="1">
+        <f t="array" ref="Q24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="R24">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="S24" cm="1">
+        <f t="array" ref="S24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="T24">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="U24" cm="1">
+        <f t="array" ref="U24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="V24">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="W24" cm="1">
+        <f t="array" ref="W24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="X24">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y24" cm="1">
+        <f t="array" ref="Y24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.2247448713915889</v>
+      </c>
+      <c r="Z24">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA24" cm="1">
+        <f t="array" ref="AA24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC24" cm="1">
+        <f t="array" ref="AC24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>192.285</v>
+      </c>
+      <c r="AE24" cm="1">
+        <f t="array" ref="AE24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>130.25277465950583</v>
+      </c>
+      <c r="AF24">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG24" cm="1">
+        <f t="array" ref="AG24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH24">
+        <f>COUNTIFS(dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <f>COUNTIFS(dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>75</v>
+      </c>
+      <c r="AK24" cm="1">
+        <f t="array" ref="AK24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>25</v>
+      </c>
+      <c r="AL24">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>25</v>
+      </c>
+      <c r="AM24" cm="1">
+        <f t="array" ref="AM24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <f>COUNTIFS(dataIntentos[Nivel],A25,dataIntentos[Intento],B25, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A25,dataIntentos[Intento],B25, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="E25" cm="1">
+        <f t="array" ref="E25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="F25">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="G25" cm="1">
+        <f t="array" ref="G25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="H25">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I25" cm="1">
+        <f t="array" ref="I25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="K25" cm="1">
+        <f t="array" ref="K25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="L25">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M25" cm="1">
+        <f t="array" ref="M25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="N25">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O25" cm="1">
+        <f t="array" ref="O25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q25" cm="1">
+        <f t="array" ref="Q25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="R25">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="S25" cm="1">
+        <f t="array" ref="S25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="T25">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U25" cm="1">
+        <f t="array" ref="U25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W25" cm="1">
+        <f t="array" ref="W25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="X25">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="Y25" cm="1">
+        <f t="array" ref="Y25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="Z25">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA25" cm="1">
+        <f t="array" ref="AA25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" cm="1">
+        <f t="array" ref="AC25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>206.09933333333333</v>
+      </c>
+      <c r="AE25" cm="1">
+        <f t="array" ref="AE25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>9.028543047222831</v>
+      </c>
+      <c r="AF25">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AG25" cm="1">
+        <f t="array" ref="AG25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <f>COUNTIFS(dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <f>COUNTIFS(dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK25" cm="1">
+        <f t="array" ref="AK25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" cm="1">
+        <f t="array" ref="AM25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <f>COUNTIFS(dataIntentos[Nivel],A26,dataIntentos[Intento],B26, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A26,dataIntentos[Intento],B26, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="E26" cm="1">
+        <f t="array" ref="E26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="F26">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G26" cm="1">
+        <f t="array" ref="G26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="H26">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="I26" cm="1">
+        <f t="array" ref="I26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="J26">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="K26" cm="1">
+        <f t="array" ref="K26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="L26">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M26" cm="1">
+        <f t="array" ref="M26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="N26">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O26" cm="1">
+        <f t="array" ref="O26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="P26">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q26" cm="1">
+        <f t="array" ref="Q26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="R26">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="S26" cm="1">
+        <f t="array" ref="S26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U26" cm="1">
+        <f t="array" ref="U26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="V26">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="W26" cm="1">
+        <f t="array" ref="W26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="X26">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Y26" cm="1">
+        <f t="array" ref="Y26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="Z26">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA26" cm="1">
+        <f t="array" ref="AA26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="AB26">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AC26" cm="1">
+        <f t="array" ref="AC26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="AD26">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>157.93833333333333</v>
+      </c>
+      <c r="AE26" cm="1">
+        <f t="array" ref="AE26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>99.431510345340499</v>
+      </c>
+      <c r="AF26">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="AG26" cm="1">
+        <f t="array" ref="AG26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>31.180478223116179</v>
+      </c>
+      <c r="AH26">
+        <f>COUNTIFS(dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <f>COUNTIFS(dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="AK26" cm="1">
+        <f t="array" ref="AK26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>23.570226039551585</v>
+      </c>
+      <c r="AL26">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="AM26" cm="1">
+        <f t="array" ref="AM26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>23.570226039551585</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <f>COUNTIFS(dataIntentos[Nivel],A27,dataIntentos[Intento],B27, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>39</v>
+      </c>
+      <c r="D27">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A27,dataIntentos[Intento],B27, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.7179487179487181</v>
+      </c>
+      <c r="E27" cm="1">
+        <f t="array" ref="E27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.7679296590705844</v>
+      </c>
+      <c r="F27">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="G27" cm="1">
+        <f t="array" ref="G27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.6794382455192631</v>
+      </c>
+      <c r="H27">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.71794871794871795</v>
+      </c>
+      <c r="I27" cm="1">
+        <f t="array" ref="I27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.78278653961403832</v>
+      </c>
+      <c r="J27">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7692307692307692</v>
+      </c>
+      <c r="K27" cm="1">
+        <f t="array" ref="K27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.5292248061679562</v>
+      </c>
+      <c r="L27">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6923076923076923</v>
+      </c>
+      <c r="M27" cm="1">
+        <f t="array" ref="M27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.60569291338552389</v>
+      </c>
+      <c r="N27">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="O27" cm="1">
+        <f t="array" ref="O27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.26646935501059649</v>
+      </c>
+      <c r="P27">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.9487179487179487</v>
+      </c>
+      <c r="Q27" cm="1">
+        <f t="array" ref="Q27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.5516528482468994</v>
+      </c>
+      <c r="R27">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3076923076923077</v>
+      </c>
+      <c r="S27" cm="1">
+        <f t="array" ref="S27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.3987878663575237</v>
+      </c>
+      <c r="T27">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.64102564102564108</v>
+      </c>
+      <c r="U27" cm="1">
+        <f t="array" ref="U27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.76751946395362902</v>
+      </c>
+      <c r="V27">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.4615384615384617</v>
+      </c>
+      <c r="W27" cm="1">
+        <f t="array" ref="W27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0339407771105615</v>
+      </c>
+      <c r="X27">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7692307692307692</v>
+      </c>
+      <c r="Y27" cm="1">
+        <f t="array" ref="Y27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0732538223823769</v>
+      </c>
+      <c r="Z27">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" cm="1">
+        <f t="array" ref="AA27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.128205128205128E-2</v>
+      </c>
+      <c r="AC27" cm="1">
+        <f t="array" ref="AC27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.22057244274468274</v>
+      </c>
+      <c r="AD27">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>190.16325641025637</v>
+      </c>
+      <c r="AE27" cm="1">
+        <f t="array" ref="AE27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>81.595655560794484</v>
+      </c>
+      <c r="AF27">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.897435897435898</v>
+      </c>
+      <c r="AG27" cm="1">
+        <f t="array" ref="AG27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>13.628392067608525</v>
+      </c>
+      <c r="AH27">
+        <f>COUNTIFS(dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+      <c r="AI27">
+        <f>COUNTIFS(dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9</v>
+      </c>
+      <c r="AJ27">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>78.13575313575312</v>
+      </c>
+      <c r="AK27" cm="1">
+        <f t="array" ref="AK27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>24.298530417398119</v>
+      </c>
+      <c r="AL27">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>21.864246864246859</v>
+      </c>
+      <c r="AM27" cm="1">
+        <f t="array" ref="AM27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>24.298530417398091</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <f>COUNTIFS(dataIntentos[Nivel],A28,dataIntentos[Intento],B28, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>24</v>
+      </c>
+      <c r="D28">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A28,dataIntentos[Intento],B28, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="E28" cm="1">
+        <f t="array" ref="E28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>3.0776975521032313</v>
+      </c>
+      <c r="F28">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.416666666666667</v>
+      </c>
+      <c r="G28" cm="1">
+        <f t="array" ref="G28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.396467307424734</v>
+      </c>
+      <c r="H28">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.75</v>
+      </c>
+      <c r="I28" cm="1">
+        <f t="array" ref="I28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.2665570127975554</v>
+      </c>
+      <c r="J28">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.0416666666666665</v>
+      </c>
+      <c r="K28" cm="1">
+        <f t="array" ref="K28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.67571978084278561</v>
+      </c>
+      <c r="L28">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.0416666666666665</v>
+      </c>
+      <c r="M28" cm="1">
+        <f t="array" ref="M28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.67571978084278561</v>
+      </c>
+      <c r="N28">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O28" cm="1">
+        <f t="array" ref="O28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.125</v>
+      </c>
+      <c r="Q28" cm="1">
+        <f t="array" ref="Q28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.7433632035635869</v>
+      </c>
+      <c r="R28">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.375</v>
+      </c>
+      <c r="S28" cm="1">
+        <f t="array" ref="S28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>2.2325713874364688</v>
+      </c>
+      <c r="T28">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.75</v>
+      </c>
+      <c r="U28" cm="1">
+        <f t="array" ref="U28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.2665570127975554</v>
+      </c>
+      <c r="V28">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.7916666666666665</v>
+      </c>
+      <c r="W28" cm="1">
+        <f t="array" ref="W28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.57584479004521882</v>
+      </c>
+      <c r="X28">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="Y28" cm="1">
+        <f t="array" ref="Y28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.6454972243679028</v>
+      </c>
+      <c r="Z28">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AA28" cm="1">
+        <f t="array" ref="AA28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.19982631347136331</v>
+      </c>
+      <c r="AB28">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AC28" cm="1">
+        <f t="array" ref="AC28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.19982631347136331</v>
+      </c>
+      <c r="AD28">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>176.38150000000005</v>
+      </c>
+      <c r="AE28" cm="1">
+        <f t="array" ref="AE28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>94.382527848555355</v>
+      </c>
+      <c r="AF28">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG28" cm="1">
+        <f t="array" ref="AG28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>14.433756729740644</v>
+      </c>
+      <c r="AH28">
+        <f>COUNTIFS(dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>15</v>
+      </c>
+      <c r="AI28">
+        <f>COUNTIFS(dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>10</v>
+      </c>
+      <c r="AJ28">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.590277777777757</v>
+      </c>
+      <c r="AK28" cm="1">
+        <f t="array" ref="AK28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>17.304595512428691</v>
+      </c>
+      <c r="AL28">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>14.409722222222213</v>
+      </c>
+      <c r="AM28" cm="1">
+        <f t="array" ref="AM28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>17.304595512428637</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <f>COUNTIFS(dataIntentos[Nivel],A29,dataIntentos[Intento],B29, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>13</v>
+      </c>
+      <c r="D29">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A29,dataIntentos[Intento],B29, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3076923076923075</v>
+      </c>
+      <c r="E29" cm="1">
+        <f t="array" ref="E29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.4349813927828945</v>
+      </c>
+      <c r="F29">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6923076923076925</v>
+      </c>
+      <c r="G29" cm="1">
+        <f t="array" ref="G29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3234346564680965</v>
+      </c>
+      <c r="H29">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="I29" cm="1">
+        <f t="array" ref="I29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.62492603112584311</v>
+      </c>
+      <c r="J29">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6923076923076923</v>
+      </c>
+      <c r="K29" cm="1">
+        <f t="array" ref="K29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="L29">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6153846153846154</v>
+      </c>
+      <c r="M29" cm="1">
+        <f t="array" ref="M29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.62492603112584311</v>
+      </c>
+      <c r="N29">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="O29" cm="1">
+        <f t="array" ref="O29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.26646935501059649</v>
+      </c>
+      <c r="P29">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6153846153846154</v>
+      </c>
+      <c r="Q29" cm="1">
+        <f t="array" ref="Q29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="R29">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="S29" cm="1">
+        <f t="array" ref="S29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.91664425290869112</v>
+      </c>
+      <c r="T29">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="U29" cm="1">
+        <f t="array" ref="U29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.63432394240271706</v>
+      </c>
+      <c r="V29">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3846153846153846</v>
+      </c>
+      <c r="W29" cm="1">
+        <f t="array" ref="W29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2113858267710478</v>
+      </c>
+      <c r="X29">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6153846153846154</v>
+      </c>
+      <c r="Y29" cm="1">
+        <f t="array" ref="Y29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="Z29">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="AA29" cm="1">
+        <f t="array" ref="AA29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.26646935501059649</v>
+      </c>
+      <c r="AB29">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AC29" cm="1">
+        <f t="array" ref="AC29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.53293871002119297</v>
+      </c>
+      <c r="AD29">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>215.25384615384613</v>
+      </c>
+      <c r="AE29" cm="1">
+        <f t="array" ref="AE29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>246.84119872340418</v>
+      </c>
+      <c r="AF29">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>84.615384615384613</v>
+      </c>
+      <c r="AG29" cm="1">
+        <f t="array" ref="AG29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>15.623150778146078</v>
+      </c>
+      <c r="AH29">
+        <f>COUNTIFS(dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7</v>
+      </c>
+      <c r="AI29">
+        <f>COUNTIFS(dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ29">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>79.230769230769226</v>
+      </c>
+      <c r="AK29" cm="1">
+        <f t="array" ref="AK29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>27.639431950631383</v>
+      </c>
+      <c r="AL29">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>20.769230769230759</v>
+      </c>
+      <c r="AM29" cm="1">
+        <f t="array" ref="AM29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>27.639431950631383</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <f>COUNTIFS(dataIntentos[Nivel],A30,dataIntentos[Intento],B30, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A30,dataIntentos[Intento],B30, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="E30" cm="1">
+        <f t="array" ref="E30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>3.7416573867739413</v>
+      </c>
+      <c r="F30">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.1111111111111107</v>
+      </c>
+      <c r="G30" cm="1">
+        <f t="array" ref="G30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.6851213274654606</v>
+      </c>
+      <c r="H30">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="I30" cm="1">
+        <f t="array" ref="I30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.1967032904743342</v>
+      </c>
+      <c r="J30">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8888888888888888</v>
+      </c>
+      <c r="K30" cm="1">
+        <f t="array" ref="K30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.99380798999990649</v>
+      </c>
+      <c r="L30">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8888888888888888</v>
+      </c>
+      <c r="M30" cm="1">
+        <f t="array" ref="M30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.99380798999990649</v>
+      </c>
+      <c r="N30">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O30" cm="1">
+        <f t="array" ref="O30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="Q30" cm="1">
+        <f t="array" ref="Q30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.922876986214646</v>
+      </c>
+      <c r="R30">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="S30" cm="1">
+        <f t="array" ref="S30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.9309052441091963</v>
+      </c>
+      <c r="T30">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="U30" cm="1">
+        <f t="array" ref="U30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.1967032904743342</v>
+      </c>
+      <c r="V30">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8888888888888888</v>
+      </c>
+      <c r="W30" cm="1">
+        <f t="array" ref="W30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.31426968052735449</v>
+      </c>
+      <c r="X30">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="Y30" cm="1">
+        <f t="array" ref="Y30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.56655772373253166</v>
+      </c>
+      <c r="Z30">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA30" cm="1">
+        <f t="array" ref="AA30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC30" cm="1">
+        <f t="array" ref="AC30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>161.08333333333337</v>
+      </c>
+      <c r="AE30" cm="1">
+        <f t="array" ref="AE30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>58.678472456070018</v>
+      </c>
+      <c r="AF30">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>86.111111111111114</v>
+      </c>
+      <c r="AG30" cm="1">
+        <f t="array" ref="AG30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.422599874998832</v>
+      </c>
+      <c r="AH30">
+        <f>COUNTIFS(dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI30">
+        <f>COUNTIFS(dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ30">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.925925925925924</v>
+      </c>
+      <c r="AK30" cm="1">
+        <f t="array" ref="AK30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>13.196312408385063</v>
+      </c>
+      <c r="AL30">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A30,dataIntentos[Intento],B30,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>14.074074074074055</v>
+      </c>
+      <c r="AM30" cm="1">
+        <f t="array" ref="AM30">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A30)*(dataIntentos[Intento]=B30)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>13.196312408385074</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <f>COUNTIFS(dataIntentos[Nivel],A31,dataIntentos[Intento],B31, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D31">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A31,dataIntentos[Intento],B31, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="E31" cm="1">
+        <f t="array" ref="E31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="F31">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="G31" cm="1">
+        <f t="array" ref="G31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="H31">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.25</v>
+      </c>
+      <c r="I31" cm="1">
+        <f t="array" ref="I31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="J31">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="K31" cm="1">
+        <f t="array" ref="K31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="L31">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M31" cm="1">
+        <f t="array" ref="M31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="N31">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O31" cm="1">
+        <f t="array" ref="O31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.75</v>
+      </c>
+      <c r="Q31" cm="1">
+        <f t="array" ref="Q31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="R31">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S31" cm="1">
+        <f t="array" ref="S31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="T31">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.25</v>
+      </c>
+      <c r="U31" cm="1">
+        <f t="array" ref="U31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="V31">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="W31" cm="1">
+        <f t="array" ref="W31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="Y31" cm="1">
+        <f t="array" ref="Y31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="Z31">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA31" cm="1">
+        <f t="array" ref="AA31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC31" cm="1">
+        <f t="array" ref="AC31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>300.40100000000001</v>
+      </c>
+      <c r="AE31" cm="1">
+        <f t="array" ref="AE31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>194.8787775528674</v>
+      </c>
+      <c r="AF31">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.75</v>
+      </c>
+      <c r="AG31" cm="1">
+        <f t="array" ref="AG31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>10.825317547305483</v>
+      </c>
+      <c r="AH31">
+        <f>COUNTIFS(dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI31">
+        <f>COUNTIFS(dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ31">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.75</v>
+      </c>
+      <c r="AK31" cm="1">
+        <f t="array" ref="AK31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>10.825317547305483</v>
+      </c>
+      <c r="AL31">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A31,dataIntentos[Intento],B31,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6.25</v>
+      </c>
+      <c r="AM31" cm="1">
+        <f t="array" ref="AM31">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A31)*(dataIntentos[Intento]=B31)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>10.825317547305483</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <f>COUNTIFS(dataIntentos[Nivel],A32,dataIntentos[Intento],B32, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A32,dataIntentos[Intento],B32, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="E32" cm="1">
+        <f t="array" ref="E32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>4.9216076867444665</v>
+      </c>
+      <c r="F32">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="G32" cm="1">
+        <f t="array" ref="G32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>3.5590260840104371</v>
+      </c>
+      <c r="H32">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I32" cm="1">
+        <f t="array" ref="I32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>2.6246692913372702</v>
+      </c>
+      <c r="J32">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="K32" cm="1">
+        <f t="array" ref="K32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="L32">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="M32" cm="1">
+        <f t="array" ref="M32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="N32">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O32" cm="1">
+        <f t="array" ref="O32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="Q32" cm="1">
+        <f t="array" ref="Q32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>3.858612300930075</v>
+      </c>
+      <c r="R32">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="S32" cm="1">
+        <f t="array" ref="S32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>3.2659863237109041</v>
+      </c>
+      <c r="T32">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="U32" cm="1">
+        <f t="array" ref="U32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>2.6246692913372702</v>
+      </c>
+      <c r="V32">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W32" cm="1">
+        <f t="array" ref="W32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="X32">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="Y32" cm="1">
+        <f t="array" ref="Y32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="Z32">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA32" cm="1">
+        <f t="array" ref="AA32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC32" cm="1">
+        <f t="array" ref="AC32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>323.9736666666667</v>
+      </c>
+      <c r="AE32" cm="1">
+        <f t="array" ref="AE32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>166.16940076587176</v>
+      </c>
+      <c r="AF32">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>83.333333333333329</v>
+      </c>
+      <c r="AG32" cm="1">
+        <f t="array" ref="AG32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.785113019775793</v>
+      </c>
+      <c r="AH32">
+        <f>COUNTIFS(dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI32">
+        <f>COUNTIFS(dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ32">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>79.166666666666671</v>
+      </c>
+      <c r="AK32" cm="1">
+        <f t="array" ref="AK32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>15.590239111558089</v>
+      </c>
+      <c r="AL32">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A32,dataIntentos[Intento],B32,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AM32" cm="1">
+        <f t="array" ref="AM32">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A32)*(dataIntentos[Intento]=B32)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>15.590239111558089</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <f>COUNTIFS(dataIntentos[Nivel],A33,dataIntentos[Intento],B33, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A33,dataIntentos[Intento],B33, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="E33" cm="1">
+        <f t="array" ref="E33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5</v>
+      </c>
+      <c r="G33" cm="1">
+        <f t="array" ref="G33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="H33">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="I33" cm="1">
+        <f t="array" ref="I33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="J33">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="K33" cm="1">
+        <f t="array" ref="K33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="M33" cm="1">
+        <f t="array" ref="M33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O33" cm="1">
+        <f t="array" ref="O33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q33" cm="1">
+        <f t="array" ref="Q33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S33" cm="1">
+        <f t="array" ref="S33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="T33">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="U33" cm="1">
+        <f t="array" ref="U33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="V33">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="W33" cm="1">
+        <f t="array" ref="W33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5</v>
+      </c>
+      <c r="Y33" cm="1">
+        <f t="array" ref="Y33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="Z33">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA33" cm="1">
+        <f t="array" ref="AA33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC33" cm="1">
+        <f t="array" ref="AC33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>107.14150000000001</v>
+      </c>
+      <c r="AE33" cm="1">
+        <f t="array" ref="AE33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>17.634499999999949</v>
+      </c>
+      <c r="AF33">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG33" cm="1">
+        <f t="array" ref="AG33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH33">
+        <f>COUNTIFS(dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI33">
+        <f>COUNTIFS(dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>90</v>
+      </c>
+      <c r="AK33" cm="1">
+        <f t="array" ref="AK33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>10</v>
+      </c>
+      <c r="AL33">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A33,dataIntentos[Intento],B33,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>10</v>
+      </c>
+      <c r="AM33" cm="1">
+        <f t="array" ref="AM33">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A33)*(dataIntentos[Intento]=B33)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87EAB2E-BA47-4739-9F5B-DD29DD1B1BA5}">
+  <dimension ref="A1:AM29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" ht="72" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIFS(dataIntentos[Nivel],A2,dataIntentos[Intento],B2, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>41</v>
+      </c>
+      <c r="D2">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A2,dataIntentos[Intento],B2, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1463414634146343</v>
+      </c>
+      <c r="E2" cm="1">
+        <f t="array" ref="E2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.6462962956767029</v>
+      </c>
+      <c r="F2">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5853658536585367</v>
+      </c>
+      <c r="G2" cm="1">
+        <f t="array" ref="G2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3964346544682573</v>
+      </c>
+      <c r="H2">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.56097560975609762</v>
+      </c>
+      <c r="I2" cm="1">
+        <f t="array" ref="I2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.0370873963643561</v>
+      </c>
+      <c r="J2">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7073170731707317</v>
+      </c>
+      <c r="K2" cm="1">
+        <f t="array" ref="K2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>1.1737765283430208</v>
+      </c>
+      <c r="L2">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5365853658536586</v>
+      </c>
+      <c r="M2" cm="1">
+        <f t="array" ref="M2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.70182900341161747</v>
+      </c>
+      <c r="N2">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.17073170731707318</v>
+      </c>
+      <c r="O2" cm="1">
+        <f t="array" ref="O2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.79333931547758996</v>
+      </c>
+      <c r="P2">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4390243902439024</v>
+      </c>
+      <c r="Q2" cm="1">
+        <f t="array" ref="Q2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0132964916019995</v>
+      </c>
+      <c r="R2">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.0487804878048781</v>
+      </c>
+      <c r="S2" cm="1">
+        <f t="array" ref="S2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.1251280580166629</v>
+      </c>
+      <c r="T2">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="U2" cm="1">
+        <f t="array" ref="U2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.53547557073414997</v>
+      </c>
+      <c r="V2">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="W2" cm="1">
+        <f t="array" ref="W2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2097167578182677</v>
+      </c>
+      <c r="X2">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3170731707317072</v>
+      </c>
+      <c r="Y2" cm="1">
+        <f t="array" ref="Y2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1778240456243547</v>
+      </c>
+      <c r="Z2">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="AA2" cm="1">
+        <f t="array" ref="AA2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.36989636312446589</v>
+      </c>
+      <c r="AB2">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="AC2" cm="1">
+        <f t="array" ref="AC2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.36989636312446589</v>
+      </c>
+      <c r="AD2">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>206.90258536585364</v>
+      </c>
+      <c r="AE2" cm="1">
+        <f t="array" ref="AE2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>70.627255894720534</v>
+      </c>
+      <c r="AF2">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.195121951219505</v>
+      </c>
+      <c r="AG2" cm="1">
+        <f t="array" ref="AG2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>16.676578452655296</v>
+      </c>
+      <c r="AH2">
+        <f>COUNTIFS(dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>13</v>
+      </c>
+      <c r="AI2">
+        <f>COUNTIFS(dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AJ2">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>83.780487804878035</v>
+      </c>
+      <c r="AK2" cm="1">
+        <f t="array" ref="AK2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>23.379815461969745</v>
+      </c>
+      <c r="AL2">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A2,dataIntentos[Intento],B2,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>16.219512195121943</v>
+      </c>
+      <c r="AM2" cm="1">
+        <f t="array" ref="AM2">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A2)*(dataIntentos[Intento]=B2)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>23.379815461969731</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <f>COUNTIFS(dataIntentos[Nivel],A3,dataIntentos[Intento],B3, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>40</v>
+      </c>
+      <c r="D3">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A3,dataIntentos[Intento],B3, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.35</v>
+      </c>
+      <c r="E3" cm="1">
+        <f t="array" ref="E3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>2.5937424698685874</v>
+      </c>
+      <c r="F3">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.65</v>
+      </c>
+      <c r="G3" cm="1">
+        <f t="array" ref="G3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.7542804792848834</v>
+      </c>
+      <c r="H3">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.7</v>
+      </c>
+      <c r="I3" cm="1">
+        <f t="array" ref="I3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.4</v>
+      </c>
+      <c r="J3">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.55</v>
+      </c>
+      <c r="K3" cm="1">
+        <f t="array" ref="K3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.86458082328952912</v>
+      </c>
+      <c r="L3">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.425</v>
+      </c>
+      <c r="M3" cm="1">
+        <f t="array" ref="M3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.77095719725546374</v>
+      </c>
+      <c r="N3">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.125</v>
+      </c>
+      <c r="O3" cm="1">
+        <f t="array" ref="O3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.39921798556678278</v>
+      </c>
+      <c r="P3">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8</v>
+      </c>
+      <c r="Q3" cm="1">
+        <f t="array" ref="Q3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.0396078054371141</v>
+      </c>
+      <c r="R3">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="S3" cm="1">
+        <f t="array" ref="S3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.2939764294607534</v>
+      </c>
+      <c r="T3">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="U3" cm="1">
+        <f t="array" ref="U3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.1594718625305229</v>
+      </c>
+      <c r="V3">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="W3" cm="1">
+        <f t="array" ref="W3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.1508149286483904</v>
+      </c>
+      <c r="X3">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="Y3" cm="1">
+        <f t="array" ref="Y3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.182951816432098</v>
+      </c>
+      <c r="Z3">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AA3" cm="1">
+        <f t="array" ref="AA3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.15612494995995996</v>
+      </c>
+      <c r="AB3">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AC3" cm="1">
+        <f t="array" ref="AC3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.15612494995995996</v>
+      </c>
+      <c r="AD3">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>192.69332500000002</v>
+      </c>
+      <c r="AE3" cm="1">
+        <f t="array" ref="AE3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>97.131850561334261</v>
+      </c>
+      <c r="AF3">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>88.75</v>
+      </c>
+      <c r="AG3" cm="1">
+        <f t="array" ref="AG3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>15.761900266148114</v>
+      </c>
+      <c r="AH3">
+        <f>COUNTIFS(dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>15</v>
+      </c>
+      <c r="AI3">
+        <f>COUNTIFS(dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="AJ3">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>79.947916666666657</v>
+      </c>
+      <c r="AK3" cm="1">
+        <f t="array" ref="AK3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>31.976579360590911</v>
+      </c>
+      <c r="AL3">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A3,dataIntentos[Intento],B3,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>20.052083333333325</v>
+      </c>
+      <c r="AM3" cm="1">
+        <f t="array" ref="AM3">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A3)*(dataIntentos[Intento]=B3)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>31.976579360590883</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <f>COUNTIFS(dataIntentos[Nivel],A4,dataIntentos[Intento],B4, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>38</v>
+      </c>
+      <c r="D4">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A4,dataIntentos[Intento],B4, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6315789473684212</v>
+      </c>
+      <c r="E4" cm="1">
+        <f t="array" ref="E4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.2859780760916437</v>
+      </c>
+      <c r="F4">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1842105263157894</v>
+      </c>
+      <c r="G4" cm="1">
+        <f t="array" ref="G4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3927493286736043</v>
+      </c>
+      <c r="H4">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.44736842105263158</v>
+      </c>
+      <c r="I4" cm="1">
+        <f t="array" ref="I4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.6765768490622337</v>
+      </c>
+      <c r="J4">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2894736842105263</v>
+      </c>
+      <c r="K4" cm="1">
+        <f t="array" ref="K4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.60297048617839999</v>
+      </c>
+      <c r="L4">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.236842105263158</v>
+      </c>
+      <c r="M4" cm="1">
+        <f t="array" ref="M4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.62551917494761644</v>
+      </c>
+      <c r="N4">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O4" cm="1">
+        <f t="array" ref="O4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.22329687826943606</v>
+      </c>
+      <c r="P4">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3421052631578947</v>
+      </c>
+      <c r="Q4" cm="1">
+        <f t="array" ref="Q4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0072452215265599</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="S4" cm="1">
+        <f t="array" ref="S4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.0989796325169001</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.39473684210526316</v>
+      </c>
+      <c r="U4" cm="1">
+        <f t="array" ref="U4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.67040732646615775</v>
+      </c>
+      <c r="V4">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7105263157894739</v>
+      </c>
+      <c r="W4" cm="1">
+        <f t="array" ref="W4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0980340023697404</v>
+      </c>
+      <c r="X4">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1052631578947367</v>
+      </c>
+      <c r="Y4" cm="1">
+        <f t="array" ref="Y4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.2729880655208237</v>
+      </c>
+      <c r="Z4">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="AA4" cm="1">
+        <f t="array" ref="AA4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.16007269816574263</v>
+      </c>
+      <c r="AB4">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="AC4" cm="1">
+        <f t="array" ref="AC4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.16007269816574263</v>
+      </c>
+      <c r="AD4">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>174.7833157894737</v>
+      </c>
+      <c r="AE4" cm="1">
+        <f t="array" ref="AE4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>53.737721293776936</v>
+      </c>
+      <c r="AF4">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>90.131578947368425</v>
+      </c>
+      <c r="AG4" cm="1">
+        <f t="array" ref="AG4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>13.498871400449469</v>
+      </c>
+      <c r="AH4">
+        <f>COUNTIFS(dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7</v>
+      </c>
+      <c r="AI4">
+        <f>COUNTIFS(dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AJ4">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.578947368421041</v>
+      </c>
+      <c r="AK4" cm="1">
+        <f t="array" ref="AK4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>26.501537438633012</v>
+      </c>
+      <c r="AL4">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A4,dataIntentos[Intento],B4,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.421052631578945</v>
+      </c>
+      <c r="AM4" cm="1">
+        <f t="array" ref="AM4">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A4)*(dataIntentos[Intento]=B4)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>26.501537438632973</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <f>COUNTIFS(dataIntentos[Nivel],A5,dataIntentos[Intento],B5, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>28</v>
+      </c>
+      <c r="D5">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A5,dataIntentos[Intento],B5, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="E5" cm="1">
+        <f t="array" ref="E5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.6174274106034645</v>
+      </c>
+      <c r="F5">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="G5" cm="1">
+        <f t="array" ref="G5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.4880476182856899</v>
+      </c>
+      <c r="H5">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.75</v>
+      </c>
+      <c r="I5" cm="1">
+        <f t="array" ref="I5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.91123934444093391</v>
+      </c>
+      <c r="J5">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2857142857142858</v>
+      </c>
+      <c r="K5" cm="1">
+        <f t="array" ref="K5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.88063057185271088</v>
+      </c>
+      <c r="L5">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.1785714285714286</v>
+      </c>
+      <c r="M5" cm="1">
+        <f t="array" ref="M5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.88856109318748067</v>
+      </c>
+      <c r="N5">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="O5" cm="1">
+        <f t="array" ref="O5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.30929478706587094</v>
+      </c>
+      <c r="P5">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4642857142857142</v>
+      </c>
+      <c r="Q5" cm="1">
+        <f t="array" ref="Q5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.2095495872768642</v>
+      </c>
+      <c r="R5">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="S5" cm="1">
+        <f t="array" ref="S5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.0708331678974965</v>
+      </c>
+      <c r="T5">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="U5" cm="1">
+        <f t="array" ref="U5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.89499743472440485</v>
+      </c>
+      <c r="V5">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="W5" cm="1">
+        <f t="array" ref="W5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.265717510476382</v>
+      </c>
+      <c r="X5">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8214285714285714</v>
+      </c>
+      <c r="Y5" cm="1">
+        <f t="array" ref="Y5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.2832317302301202</v>
+      </c>
+      <c r="Z5">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" cm="1">
+        <f t="array" ref="AA5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC5" cm="1">
+        <f t="array" ref="AC5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>182.15225000000001</v>
+      </c>
+      <c r="AE5" cm="1">
+        <f t="array" ref="AE5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>91.531177182432202</v>
+      </c>
+      <c r="AF5">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.714285714285708</v>
+      </c>
+      <c r="AG5" cm="1">
+        <f t="array" ref="AG5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>14.060728346449663</v>
+      </c>
+      <c r="AH5">
+        <f>COUNTIFS(dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AI5">
+        <f>COUNTIFS(dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>72.193877551020393</v>
+      </c>
+      <c r="AK5" cm="1">
+        <f t="array" ref="AK5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>32.276828208862113</v>
+      </c>
+      <c r="AL5">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A5,dataIntentos[Intento],B5,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>27.806122448979583</v>
+      </c>
+      <c r="AM5" cm="1">
+        <f t="array" ref="AM5">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A5)*(dataIntentos[Intento]=B5)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>32.276828208862106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f>COUNTIFS(dataIntentos[Nivel],A6,dataIntentos[Intento],B6, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A6,dataIntentos[Intento],B6, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7692307692307692</v>
+      </c>
+      <c r="E6" cm="1">
+        <f t="array" ref="E6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.2802551520840952</v>
+      </c>
+      <c r="F6">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2307692307692308</v>
+      </c>
+      <c r="G6" cm="1">
+        <f t="array" ref="G6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.2498520622516862</v>
+      </c>
+      <c r="H6">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="I6" cm="1">
+        <f t="array" ref="I6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.0462669622104188</v>
+      </c>
+      <c r="J6">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3461538461538463</v>
+      </c>
+      <c r="K6" cm="1">
+        <f t="array" ref="K6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.61658536699543831</v>
+      </c>
+      <c r="L6">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3076923076923077</v>
+      </c>
+      <c r="M6" cm="1">
+        <f t="array" ref="M6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.66617338752649125</v>
+      </c>
+      <c r="N6">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="O6" cm="1">
+        <f t="array" ref="O6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="P6">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4230769230769231</v>
+      </c>
+      <c r="Q6" cm="1">
+        <f t="array" ref="Q6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0803516850144723</v>
+      </c>
+      <c r="R6">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="S6" cm="1">
+        <f t="array" ref="S6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.87367820704619592</v>
+      </c>
+      <c r="T6">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="U6" cm="1">
+        <f t="array" ref="U6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.0469736606781692</v>
+      </c>
+      <c r="V6">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3846153846153846</v>
+      </c>
+      <c r="W6" cm="1">
+        <f t="array" ref="W6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2113858267710478</v>
+      </c>
+      <c r="X6">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7307692307692308</v>
+      </c>
+      <c r="Y6" cm="1">
+        <f t="array" ref="Y6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1285692885477854</v>
+      </c>
+      <c r="Z6">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" cm="1">
+        <f t="array" ref="AA6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC6" cm="1">
+        <f t="array" ref="AC6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>183.06</v>
+      </c>
+      <c r="AE6" cm="1">
+        <f t="array" ref="AE6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>87.715579105249148</v>
+      </c>
+      <c r="AF6">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>91.34615384615384</v>
+      </c>
+      <c r="AG6" cm="1">
+        <f t="array" ref="AG6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.893573920050944</v>
+      </c>
+      <c r="AH6">
+        <f>COUNTIFS(dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6</v>
+      </c>
+      <c r="AI6">
+        <f>COUNTIFS(dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ6">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.089743589743577</v>
+      </c>
+      <c r="AK6" cm="1">
+        <f t="array" ref="AK6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>31.398807437246159</v>
+      </c>
+      <c r="AL6">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A6,dataIntentos[Intento],B6,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.910256410256409</v>
+      </c>
+      <c r="AM6" cm="1">
+        <f t="array" ref="AM6">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A6)*(dataIntentos[Intento]=B6)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>31.39880743724612</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <f>COUNTIFS(dataIntentos[Nivel],A7,dataIntentos[Intento],B7, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A7,dataIntentos[Intento],B7, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.6111111111111112</v>
+      </c>
+      <c r="E7" cm="1">
+        <f t="array" ref="E7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.37997137204158</v>
+      </c>
+      <c r="F7">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="G7" cm="1">
+        <f t="array" ref="G7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.4098419489388356</v>
+      </c>
+      <c r="H7">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="I7" cm="1">
+        <f t="array" ref="I7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="J7">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6111111111111112</v>
+      </c>
+      <c r="K7" cm="1">
+        <f t="array" ref="K7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.48749802152178456</v>
+      </c>
+      <c r="L7">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="M7" cm="1">
+        <f t="array" ref="M7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.49690399499995325</v>
+      </c>
+      <c r="N7">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="O7" cm="1">
+        <f t="array" ref="O7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.22906142364542559</v>
+      </c>
+      <c r="P7">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q7" cm="1">
+        <f t="array" ref="Q7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="R7">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="S7" cm="1">
+        <f t="array" ref="S7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.11665284679121</v>
+      </c>
+      <c r="T7">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="U7" cm="1">
+        <f t="array" ref="U7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.1653431646335017</v>
+      </c>
+      <c r="V7">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7222222222222223</v>
+      </c>
+      <c r="W7" cm="1">
+        <f t="array" ref="W7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0957268290731121</v>
+      </c>
+      <c r="X7">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y7" cm="1">
+        <f t="array" ref="Y7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0540925533894598</v>
+      </c>
+      <c r="Z7">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" cm="1">
+        <f t="array" ref="AA7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" cm="1">
+        <f t="array" ref="AC7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>178.98477777777782</v>
+      </c>
+      <c r="AE7" cm="1">
+        <f t="array" ref="AE7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>57.451810645053229</v>
+      </c>
+      <c r="AF7">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.055555555555557</v>
+      </c>
+      <c r="AG7" cm="1">
+        <f t="array" ref="AG7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.197580205970208</v>
+      </c>
+      <c r="AH7">
+        <f>COUNTIFS(dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI7">
+        <f>COUNTIFS(dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ7">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>88.425925925925924</v>
+      </c>
+      <c r="AK7" cm="1">
+        <f t="array" ref="AK7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>22.246321808766616</v>
+      </c>
+      <c r="AL7">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A7,dataIntentos[Intento],B7,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>11.574074074074073</v>
+      </c>
+      <c r="AM7" cm="1">
+        <f t="array" ref="AM7">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A7)*(dataIntentos[Intento]=B7)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>22.246321808766591</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <f>COUNTIFS(dataIntentos[Nivel],A8,dataIntentos[Intento],B8, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A8,dataIntentos[Intento],B8, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="E8" cm="1">
+        <f t="array" ref="E8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>2.411706145162019</v>
+      </c>
+      <c r="F8">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.6659862556700857</v>
+      </c>
+      <c r="H8">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I8" cm="1">
+        <f t="array" ref="I8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.1866605518454392</v>
+      </c>
+      <c r="J8">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="K8" cm="1">
+        <f t="array" ref="K8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.49487165930539351</v>
+      </c>
+      <c r="L8">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M8" cm="1">
+        <f t="array" ref="M8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.62678317052800869</v>
+      </c>
+      <c r="N8">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="O8" cm="1">
+        <f t="array" ref="O8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.25753937681885641</v>
+      </c>
+      <c r="P8">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q8" cm="1">
+        <f t="array" ref="Q8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.2677868380553634</v>
+      </c>
+      <c r="R8">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2142857142857142</v>
+      </c>
+      <c r="S8" cm="1">
+        <f t="array" ref="S8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.5202711895566259</v>
+      </c>
+      <c r="T8">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="U8" cm="1">
+        <f t="array" ref="U8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.2058530725810095</v>
+      </c>
+      <c r="V8">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="W8" cm="1">
+        <f t="array" ref="W8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2371791482634837</v>
+      </c>
+      <c r="X8">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y8" cm="1">
+        <f t="array" ref="Y8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1952286093343936</v>
+      </c>
+      <c r="Z8">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" cm="1">
+        <f t="array" ref="AA8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC8" cm="1">
+        <f t="array" ref="AC8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>197.20271428571431</v>
+      </c>
+      <c r="AE8" cm="1">
+        <f t="array" ref="AE8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>96.956797791909437</v>
+      </c>
+      <c r="AF8">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG8" cm="1">
+        <f t="array" ref="AG8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH8">
+        <f>COUNTIFS(dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="AI8">
+        <f>COUNTIFS(dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>77.414965986394549</v>
+      </c>
+      <c r="AK8" cm="1">
+        <f t="array" ref="AK8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>27.697352218452188</v>
+      </c>
+      <c r="AL8">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A8,dataIntentos[Intento],B8,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>22.58503401360543</v>
+      </c>
+      <c r="AM8" cm="1">
+        <f t="array" ref="AM8">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A8)*(dataIntentos[Intento]=B8)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>27.697352218452195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <f>COUNTIFS(dataIntentos[Nivel],A9,dataIntentos[Intento],B9, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A9,dataIntentos[Intento],B9, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.2222222222222223</v>
+      </c>
+      <c r="E9" cm="1">
+        <f t="array" ref="E9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.3146843962443591</v>
+      </c>
+      <c r="F9">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="G9" cm="1">
+        <f t="array" ref="G9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="H9">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="I9" cm="1">
+        <f t="array" ref="I9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.41573970964154905</v>
+      </c>
+      <c r="J9">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="K9" cm="1">
+        <f t="array" ref="K9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.6849348892187751</v>
+      </c>
+      <c r="L9">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5555555555555556</v>
+      </c>
+      <c r="M9" cm="1">
+        <f t="array" ref="M9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.6849348892187751</v>
+      </c>
+      <c r="N9">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O9" cm="1">
+        <f t="array" ref="O9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Q9" cm="1">
+        <f t="array" ref="Q9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="R9">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4444444444444444</v>
+      </c>
+      <c r="S9" cm="1">
+        <f t="array" ref="S9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.4229164972072998</v>
+      </c>
+      <c r="T9">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U9" cm="1">
+        <f t="array" ref="U9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.41573970964154905</v>
+      </c>
+      <c r="V9">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="W9" cm="1">
+        <f t="array" ref="W9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0999438818457405</v>
+      </c>
+      <c r="X9">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="Y9" cm="1">
+        <f t="array" ref="Y9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0540925533894598</v>
+      </c>
+      <c r="Z9">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" cm="1">
+        <f t="array" ref="AA9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC9" cm="1">
+        <f t="array" ref="AC9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>185.7378888888889</v>
+      </c>
+      <c r="AE9" cm="1">
+        <f t="array" ref="AE9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>52.788105329903466</v>
+      </c>
+      <c r="AF9">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>94.444444444444443</v>
+      </c>
+      <c r="AG9" cm="1">
+        <f t="array" ref="AG9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>10.393492741038726</v>
+      </c>
+      <c r="AH9">
+        <f>COUNTIFS(dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f>COUNTIFS(dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>91.666666666666671</v>
+      </c>
+      <c r="AK9" cm="1">
+        <f t="array" ref="AK9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="AL9">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A9,dataIntentos[Intento],B9,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="AM9" cm="1">
+        <f t="array" ref="AM9">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A9)*(dataIntentos[Intento]=B9)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>16.666666666666668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <f>COUNTIFS(dataIntentos[Nivel],A10,dataIntentos[Intento],B10, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A10,dataIntentos[Intento],B10, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="E10" cm="1">
+        <f t="array" ref="E10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.1989578808281798</v>
+      </c>
+      <c r="F10">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.125</v>
+      </c>
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3635890143294642</v>
+      </c>
+      <c r="H10">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.125</v>
+      </c>
+      <c r="I10" cm="1">
+        <f t="array" ref="I10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.33071891388307384</v>
+      </c>
+      <c r="J10">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.625</v>
+      </c>
+      <c r="K10" cm="1">
+        <f t="array" ref="K10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.48412291827592713</v>
+      </c>
+      <c r="L10">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.625</v>
+      </c>
+      <c r="M10" cm="1">
+        <f t="array" ref="M10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.48412291827592713</v>
+      </c>
+      <c r="N10">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O10" cm="1">
+        <f t="array" ref="O10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.625</v>
+      </c>
+      <c r="Q10" cm="1">
+        <f t="array" ref="Q10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.85695682505013049</v>
+      </c>
+      <c r="R10">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S10" cm="1">
+        <f t="array" ref="S10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.125</v>
+      </c>
+      <c r="U10" cm="1">
+        <f t="array" ref="U10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.33071891388307384</v>
+      </c>
+      <c r="V10">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.125</v>
+      </c>
+      <c r="W10" cm="1">
+        <f t="array" ref="W10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.78062474979979979</v>
+      </c>
+      <c r="X10">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="Y10" cm="1">
+        <f t="array" ref="Y10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1989578808281798</v>
+      </c>
+      <c r="Z10">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" cm="1">
+        <f t="array" ref="AA10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC10" cm="1">
+        <f t="array" ref="AC10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>176.21562500000002</v>
+      </c>
+      <c r="AE10" cm="1">
+        <f t="array" ref="AE10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>58.38293383116654</v>
+      </c>
+      <c r="AF10">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>96.875</v>
+      </c>
+      <c r="AG10" cm="1">
+        <f t="array" ref="AG10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>8.2679728470768463</v>
+      </c>
+      <c r="AH10">
+        <f>COUNTIFS(dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <f>COUNTIFS(dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.75</v>
+      </c>
+      <c r="AK10" cm="1">
+        <f t="array" ref="AK10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>16.535945694153693</v>
+      </c>
+      <c r="AL10">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A10,dataIntentos[Intento],B10,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6.25</v>
+      </c>
+      <c r="AM10" cm="1">
+        <f t="array" ref="AM10">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A10)*(dataIntentos[Intento]=B10)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>16.535945694153693</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4">
+        <f>COUNTIFS(dataIntentos[Nivel],A11,dataIntentos[Intento],B11, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A11,dataIntentos[Intento],B11, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="E11" cm="1">
+        <f t="array" ref="E11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.6329931618554521</v>
+      </c>
+      <c r="F11">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="G11" cm="1">
+        <f t="array" ref="G11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.0548046676563256</v>
+      </c>
+      <c r="H11">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I11" cm="1">
+        <f t="array" ref="I11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="J11">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="K11" cm="1">
+        <f t="array" ref="K11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="L11">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="M11" cm="1">
+        <f t="array" ref="M11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="N11">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O11" cm="1">
+        <f t="array" ref="O11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="P11">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Q11" cm="1">
+        <f t="array" ref="Q11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="R11">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="S11" cm="1">
+        <f t="array" ref="S11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="T11">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U11" cm="1">
+        <f t="array" ref="U11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="V11">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="W11" cm="1">
+        <f t="array" ref="W11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.8856180831641267</v>
+      </c>
+      <c r="X11">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Y11" cm="1">
+        <f t="array" ref="Y11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="Z11">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AA11" cm="1">
+        <f t="array" ref="AA11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="AB11">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AC11" cm="1">
+        <f t="array" ref="AC11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="AD11">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>161.75333333333333</v>
+      </c>
+      <c r="AE11" cm="1">
+        <f t="array" ref="AE11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>38.489508582065433</v>
+      </c>
+      <c r="AF11">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>75</v>
+      </c>
+      <c r="AG11" cm="1">
+        <f t="array" ref="AG11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>20.412414523193153</v>
+      </c>
+      <c r="AH11">
+        <f>COUNTIFS(dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <f>COUNTIFS(dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>55.555555555555536</v>
+      </c>
+      <c r="AK11" cm="1">
+        <f t="array" ref="AK11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>41.573970964154888</v>
+      </c>
+      <c r="AL11">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A11,dataIntentos[Intento],B11,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>44.444444444444436</v>
+      </c>
+      <c r="AM11" cm="1">
+        <f t="array" ref="AM11">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A11)*(dataIntentos[Intento]=B11)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>41.573970964154903</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(dataIntentos[Nivel],A12,dataIntentos[Intento],B12, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>49</v>
+      </c>
+      <c r="D12">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A12,dataIntentos[Intento],B12, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.2448979591836733</v>
+      </c>
+      <c r="E12" cm="1">
+        <f t="array" ref="E12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.4642768256858856</v>
+      </c>
+      <c r="F12">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7551020408163267</v>
+      </c>
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.597582513533137</v>
+      </c>
+      <c r="H12">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.48979591836734693</v>
+      </c>
+      <c r="I12" cm="1">
+        <f t="array" ref="I12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.83598772033730784</v>
+      </c>
+      <c r="J12">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7755102040816326</v>
+      </c>
+      <c r="K12" cm="1">
+        <f t="array" ref="K12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.86343656331861951</v>
+      </c>
+      <c r="L12">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6326530612244898</v>
+      </c>
+      <c r="M12" cm="1">
+        <f t="array" ref="M12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.91904736728144509</v>
+      </c>
+      <c r="N12">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O12" cm="1">
+        <f t="array" ref="O12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.40406101782088427</v>
+      </c>
+      <c r="P12">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4693877551020409</v>
+      </c>
+      <c r="Q12" cm="1">
+        <f t="array" ref="Q12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0321770299103503</v>
+      </c>
+      <c r="R12">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.1224489795918366</v>
+      </c>
+      <c r="S12" cm="1">
+        <f t="array" ref="S12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.0997709049230595</v>
+      </c>
+      <c r="T12">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.34693877551020408</v>
+      </c>
+      <c r="U12" cm="1">
+        <f t="array" ref="U12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.59078019698490325</v>
+      </c>
+      <c r="V12">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3673469387755102</v>
+      </c>
+      <c r="W12" cm="1">
+        <f t="array" ref="W12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.84982297198600054</v>
+      </c>
+      <c r="X12">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="Y12" cm="1">
+        <f t="array" ref="Y12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="Z12">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.44897959183673469</v>
+      </c>
+      <c r="AA12" cm="1">
+        <f t="array" ref="AA12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.70163728317024832</v>
+      </c>
+      <c r="AB12">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AC12" cm="1">
+        <f t="array" ref="AC12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.88063057185271088</v>
+      </c>
+      <c r="AD12">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>256.78400000000005</v>
+      </c>
+      <c r="AE12" cm="1">
+        <f t="array" ref="AE12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>114.92059284691187</v>
+      </c>
+      <c r="AF12">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.122448979591837</v>
+      </c>
+      <c r="AG12" cm="1">
+        <f t="array" ref="AG12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>20.535318160712354</v>
+      </c>
+      <c r="AH12">
+        <f>COUNTIFS(dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>22</v>
+      </c>
+      <c r="AI12">
+        <f>COUNTIFS(dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="AJ12">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.103012633624886</v>
+      </c>
+      <c r="AK12" cm="1">
+        <f t="array" ref="AK12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>31.355699814623836</v>
+      </c>
+      <c r="AL12">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A12,dataIntentos[Intento],B12,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.896987366375111</v>
+      </c>
+      <c r="AM12" cm="1">
+        <f t="array" ref="AM12">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A12)*(dataIntentos[Intento]=B12)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>31.355699814623875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(dataIntentos[Nivel],A13,dataIntentos[Intento],B13, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A13,dataIntentos[Intento],B13, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5384615384615383</v>
+      </c>
+      <c r="E13" cm="1">
+        <f t="array" ref="E13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.0462669622104188</v>
+      </c>
+      <c r="F13">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3076923076923075</v>
+      </c>
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.1013708510212579</v>
+      </c>
+      <c r="H13">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="I13" cm="1">
+        <f t="array" ref="I13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.42132504423474315</v>
+      </c>
+      <c r="J13">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8461538461538463</v>
+      </c>
+      <c r="K13" cm="1">
+        <f t="array" ref="K13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.45508306023843198</v>
+      </c>
+      <c r="L13">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8076923076923077</v>
+      </c>
+      <c r="M13" cm="1">
+        <f t="array" ref="M13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.48192169562083337</v>
+      </c>
+      <c r="N13">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="O13" cm="1">
+        <f t="array" ref="O13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="P13">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6923076923076923</v>
+      </c>
+      <c r="Q13" cm="1">
+        <f t="array" ref="Q13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.82131371169471623</v>
+      </c>
+      <c r="R13">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S13" cm="1">
+        <f t="array" ref="S13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.88795356773963041</v>
+      </c>
+      <c r="T13">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="U13" cm="1">
+        <f t="array" ref="U13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.39411349099844606</v>
+      </c>
+      <c r="V13">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.7307692307692308</v>
+      </c>
+      <c r="W13" cm="1">
+        <f t="array" ref="W13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.44356009979503064</v>
+      </c>
+      <c r="X13">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3846153846153846</v>
+      </c>
+      <c r="Y13" cm="1">
+        <f t="array" ref="Y13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1461280327501031</v>
+      </c>
+      <c r="Z13">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AA13" cm="1">
+        <f t="array" ref="AA13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.57563959796522179</v>
+      </c>
+      <c r="AB13">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="AC13" cm="1">
+        <f t="array" ref="AC13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.71023789663920722</v>
+      </c>
+      <c r="AD13">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>353.86403846153854</v>
+      </c>
+      <c r="AE13" cm="1">
+        <f t="array" ref="AE13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>566.12742751905648</v>
+      </c>
+      <c r="AF13">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>90.384615384615387</v>
+      </c>
+      <c r="AG13" cm="1">
+        <f t="array" ref="AG13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>14.000211325539457</v>
+      </c>
+      <c r="AH13">
+        <f>COUNTIFS(dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>16</v>
+      </c>
+      <c r="AI13">
+        <f>COUNTIFS(dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>11</v>
+      </c>
+      <c r="AJ13">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.012820512820497</v>
+      </c>
+      <c r="AK13" cm="1">
+        <f t="array" ref="AK13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>13.697114540864565</v>
+      </c>
+      <c r="AL13">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A13,dataIntentos[Intento],B13,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6.9871794871794846</v>
+      </c>
+      <c r="AM13" cm="1">
+        <f t="array" ref="AM13">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A13)*(dataIntentos[Intento]=B13)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>13.697114540864508</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <f>COUNTIFS(dataIntentos[Nivel],A14,dataIntentos[Intento],B14, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A14,dataIntentos[Intento],B14, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="E14" cm="1">
+        <f t="array" ref="E14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.2133516482134197</v>
+      </c>
+      <c r="F14">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5833333333333335</v>
+      </c>
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3202482931462383</v>
+      </c>
+      <c r="H14">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.25</v>
+      </c>
+      <c r="I14" cm="1">
+        <f t="array" ref="I14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="J14">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5833333333333333</v>
+      </c>
+      <c r="K14" cm="1">
+        <f t="array" ref="K14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.75920279826202486</v>
+      </c>
+      <c r="L14">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M14" cm="1">
+        <f t="array" ref="M14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.76376261582597338</v>
+      </c>
+      <c r="N14">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="O14" cm="1">
+        <f t="array" ref="O14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.27638539919628335</v>
+      </c>
+      <c r="P14">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q14" cm="1">
+        <f t="array" ref="Q14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.59511903571190417</v>
+      </c>
+      <c r="R14">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.0833333333333333</v>
+      </c>
+      <c r="S14" cm="1">
+        <f t="array" ref="S14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.75920279826202486</v>
+      </c>
+      <c r="T14">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U14" cm="1">
+        <f t="array" ref="U14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.37267799624996495</v>
+      </c>
+      <c r="V14">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="W14" cm="1">
+        <f t="array" ref="W14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.1426091000668408</v>
+      </c>
+      <c r="X14">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Y14" cm="1">
+        <f t="array" ref="Y14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0274023338281628</v>
+      </c>
+      <c r="Z14">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA14" cm="1">
+        <f t="array" ref="AA14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.62360956446232352</v>
+      </c>
+      <c r="AB14">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AC14" cm="1">
+        <f t="array" ref="AC14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.62360956446232352</v>
+      </c>
+      <c r="AD14">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>221.69291666666666</v>
+      </c>
+      <c r="AE14" cm="1">
+        <f t="array" ref="AE14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>100.58739560489862</v>
+      </c>
+      <c r="AF14">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG14" cm="1">
+        <f t="array" ref="AG14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH14">
+        <f>COUNTIFS(dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI14">
+        <f>COUNTIFS(dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>86.805555555555543</v>
+      </c>
+      <c r="AK14" cm="1">
+        <f t="array" ref="AK14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>28.353410642491156</v>
+      </c>
+      <c r="AL14">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A14,dataIntentos[Intento],B14,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>13.194444444444443</v>
+      </c>
+      <c r="AM14" cm="1">
+        <f t="array" ref="AM14">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A14)*(dataIntentos[Intento]=B14)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>28.353410642491113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <f>COUNTIFS(dataIntentos[Nivel],A15,dataIntentos[Intento],B15, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A15,dataIntentos[Intento],B15, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.0909090909090908</v>
+      </c>
+      <c r="E15" cm="1">
+        <f t="array" ref="E15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.311109554714178</v>
+      </c>
+      <c r="F15">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6363636363636362</v>
+      </c>
+      <c r="G15" cm="1">
+        <f t="array" ref="G15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3666633071248098</v>
+      </c>
+      <c r="H15">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="I15" cm="1">
+        <f t="array" ref="I15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.655554777357089</v>
+      </c>
+      <c r="J15">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6363636363636365</v>
+      </c>
+      <c r="K15" cm="1">
+        <f t="array" ref="K15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.77138921583987008</v>
+      </c>
+      <c r="L15">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4545454545454546</v>
+      </c>
+      <c r="M15" cm="1">
+        <f t="array" ref="M15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.655554777357089</v>
+      </c>
+      <c r="N15">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="O15" cm="1">
+        <f t="array" ref="O15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.57495957457606894</v>
+      </c>
+      <c r="P15">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4545454545454546</v>
+      </c>
+      <c r="Q15" cm="1">
+        <f t="array" ref="Q15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.89072354283024657</v>
+      </c>
+      <c r="R15">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.1818181818181819</v>
+      </c>
+      <c r="S15" cm="1">
+        <f t="array" ref="S15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.93596637645336367</v>
+      </c>
+      <c r="T15">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U15" cm="1">
+        <f t="array" ref="U15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.44536177141512329</v>
+      </c>
+      <c r="V15">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1818181818181817</v>
+      </c>
+      <c r="W15" cm="1">
+        <f t="array" ref="W15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.1134044285378082</v>
+      </c>
+      <c r="X15">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8181818181818181</v>
+      </c>
+      <c r="Y15" cm="1">
+        <f t="array" ref="Y15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1922615498730911</v>
+      </c>
+      <c r="Z15">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="AA15" cm="1">
+        <f t="array" ref="AA15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.28747978728803447</v>
+      </c>
+      <c r="AB15">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AC15" cm="1">
+        <f t="array" ref="AC15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.38569460791993504</v>
+      </c>
+      <c r="AD15">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>199.15018181818184</v>
+      </c>
+      <c r="AE15" cm="1">
+        <f t="array" ref="AE15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>82.015212675141896</v>
+      </c>
+      <c r="AF15">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>88.63636363636364</v>
+      </c>
+      <c r="AG15" cm="1">
+        <f t="array" ref="AG15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.44823994329923</v>
+      </c>
+      <c r="AH15">
+        <f>COUNTIFS(dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI15">
+        <f>COUNTIFS(dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="AJ15">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>81.515151515151516</v>
+      </c>
+      <c r="AK15" cm="1">
+        <f t="array" ref="AK15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>30.529457090318004</v>
+      </c>
+      <c r="AL15">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A15,dataIntentos[Intento],B15,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>18.484848484848484</v>
+      </c>
+      <c r="AM15" cm="1">
+        <f t="array" ref="AM15">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A15)*(dataIntentos[Intento]=B15)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>30.529457090318004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <f>COUNTIFS(dataIntentos[Nivel],A16,dataIntentos[Intento],B16, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A16,dataIntentos[Intento],B16, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="E16" cm="1">
+        <f t="array" ref="E16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.68718427093627676</v>
+      </c>
+      <c r="F16">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="G16" cm="1">
+        <f t="array" ref="G16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.68718427093627676</v>
+      </c>
+      <c r="H16">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" cm="1">
+        <f t="array" ref="I16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="K16" cm="1">
+        <f t="array" ref="K16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="L16">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M16" cm="1">
+        <f t="array" ref="M16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="N16">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O16" cm="1">
+        <f t="array" ref="O16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Q16" cm="1">
+        <f t="array" ref="Q16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.37267799624996495</v>
+      </c>
+      <c r="R16">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="S16" cm="1">
+        <f t="array" ref="S16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.37267799624996495</v>
+      </c>
+      <c r="T16">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U16" cm="1">
+        <f t="array" ref="U16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W16" cm="1">
+        <f t="array" ref="W16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.7453559924999299</v>
+      </c>
+      <c r="X16">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y16" cm="1">
+        <f t="array" ref="Y16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA16" cm="1">
+        <f t="array" ref="AA16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="AB16">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AC16" cm="1">
+        <f t="array" ref="AC16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="AD16">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>236.47566666666668</v>
+      </c>
+      <c r="AE16" cm="1">
+        <f t="array" ref="AE16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>22.077209218759709</v>
+      </c>
+      <c r="AF16">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>91.666666666666671</v>
+      </c>
+      <c r="AG16" cm="1">
+        <f t="array" ref="AG16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.785113019775793</v>
+      </c>
+      <c r="AH16">
+        <f>COUNTIFS(dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <f>COUNTIFS(dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK16" cm="1">
+        <f t="array" ref="AK16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A16,dataIntentos[Intento],B16,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM16" cm="1">
+        <f t="array" ref="AM16">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A16)*(dataIntentos[Intento]=B16)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <f>COUNTIFS(dataIntentos[Nivel],A17,dataIntentos[Intento],B17, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A17,dataIntentos[Intento],B17, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="E17" cm="1">
+        <f t="array" ref="E17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="F17">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="G17" cm="1">
+        <f t="array" ref="G17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="H17">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I17" cm="1">
+        <f t="array" ref="I17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="K17" cm="1">
+        <f t="array" ref="K17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="L17">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M17" cm="1">
+        <f t="array" ref="M17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="N17">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O17" cm="1">
+        <f t="array" ref="O17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="Q17" cm="1">
+        <f t="array" ref="Q17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="R17">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="S17" cm="1">
+        <f t="array" ref="S17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="T17">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U17" cm="1">
+        <f t="array" ref="U17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="W17" cm="1">
+        <f t="array" ref="W17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="X17">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5</v>
+      </c>
+      <c r="Y17" cm="1">
+        <f t="array" ref="Y17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1180339887498949</v>
+      </c>
+      <c r="Z17">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" cm="1">
+        <f t="array" ref="AA17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" cm="1">
+        <f t="array" ref="AC17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>209.43324999999999</v>
+      </c>
+      <c r="AE17" cm="1">
+        <f t="array" ref="AE17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>74.057046141386877</v>
+      </c>
+      <c r="AF17">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AG17" cm="1">
+        <f t="array" ref="AG17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <f>COUNTIFS(dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <f>COUNTIFS(dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK17" cm="1">
+        <f t="array" ref="AK17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A17,dataIntentos[Intento],B17,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM17" cm="1">
+        <f t="array" ref="AM17">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A17)*(dataIntentos[Intento]=B17)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <f>COUNTIFS(dataIntentos[Nivel],A18,dataIntentos[Intento],B18, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A18,dataIntentos[Intento],B18, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="E18" cm="1">
+        <f t="array" ref="E18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.0897247358851685</v>
+      </c>
+      <c r="F18">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="G18" cm="1">
+        <f t="array" ref="G18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.0897247358851685</v>
+      </c>
+      <c r="H18">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I18" cm="1">
+        <f t="array" ref="I18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="K18" cm="1">
+        <f t="array" ref="K18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="L18">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="M18" cm="1">
+        <f t="array" ref="M18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="N18">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O18" cm="1">
+        <f t="array" ref="O18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="Q18" cm="1">
+        <f t="array" ref="Q18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="R18">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="S18" cm="1">
+        <f t="array" ref="S18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="T18">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U18" cm="1">
+        <f t="array" ref="U18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="W18" cm="1">
+        <f t="array" ref="W18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="X18">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.5</v>
+      </c>
+      <c r="Y18" cm="1">
+        <f t="array" ref="Y18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1180339887498949</v>
+      </c>
+      <c r="Z18">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" cm="1">
+        <f t="array" ref="AA18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" cm="1">
+        <f t="array" ref="AC18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>182.77575000000002</v>
+      </c>
+      <c r="AE18" cm="1">
+        <f t="array" ref="AE18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>102.49415469034074</v>
+      </c>
+      <c r="AF18">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AG18" cm="1">
+        <f t="array" ref="AG18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <f>COUNTIFS(dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <f>COUNTIFS(dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK18" cm="1">
+        <f t="array" ref="AK18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A18,dataIntentos[Intento],B18,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM18" cm="1">
+        <f t="array" ref="AM18">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A18)*(dataIntentos[Intento]=B18)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <f>COUNTIFS(dataIntentos[Nivel],A19,dataIntentos[Intento],B19, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A19,dataIntentos[Intento],B19, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8</v>
+      </c>
+      <c r="E19" cm="1">
+        <f t="array" ref="E19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>3.2496153618543842</v>
+      </c>
+      <c r="F19">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6</v>
+      </c>
+      <c r="G19" cm="1">
+        <f t="array" ref="G19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.1540659228538015</v>
+      </c>
+      <c r="H19">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.2</v>
+      </c>
+      <c r="I19" cm="1">
+        <f t="array" ref="I19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.6</v>
+      </c>
+      <c r="J19">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.4</v>
+      </c>
+      <c r="K19" cm="1">
+        <f t="array" ref="K19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>1.8547236990991407</v>
+      </c>
+      <c r="L19">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M19" cm="1">
+        <f t="array" ref="M19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>2.0396078054371141</v>
+      </c>
+      <c r="N19">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.2</v>
+      </c>
+      <c r="O19" cm="1">
+        <f t="array" ref="O19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.4</v>
+      </c>
+      <c r="P19">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.4</v>
+      </c>
+      <c r="Q19" cm="1">
+        <f t="array" ref="Q19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.4966629547095767</v>
+      </c>
+      <c r="R19">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.4</v>
+      </c>
+      <c r="S19" cm="1">
+        <f t="array" ref="S19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.8</v>
+      </c>
+      <c r="T19">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="U19" cm="1">
+        <f t="array" ref="U19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.5491933384829668</v>
+      </c>
+      <c r="V19">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="W19" cm="1">
+        <f t="array" ref="W19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2649110640673518</v>
+      </c>
+      <c r="X19">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.8</v>
+      </c>
+      <c r="Y19" cm="1">
+        <f t="array" ref="Y19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.1661903789690602</v>
+      </c>
+      <c r="Z19">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA19" cm="1">
+        <f t="array" ref="AA19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.2</v>
+      </c>
+      <c r="AC19" cm="1">
+        <f t="array" ref="AC19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.4</v>
+      </c>
+      <c r="AD19">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>199.17119999999997</v>
+      </c>
+      <c r="AE19" cm="1">
+        <f t="array" ref="AE19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>200.19441443197161</v>
+      </c>
+      <c r="AF19">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85</v>
+      </c>
+      <c r="AG19" cm="1">
+        <f t="array" ref="AG19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>20</v>
+      </c>
+      <c r="AH19">
+        <f>COUNTIFS(dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <f>COUNTIFS(dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>72</v>
+      </c>
+      <c r="AK19" cm="1">
+        <f t="array" ref="AK19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>39.191835884530846</v>
+      </c>
+      <c r="AL19">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A19,dataIntentos[Intento],B19,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>28</v>
+      </c>
+      <c r="AM19" cm="1">
+        <f t="array" ref="AM19">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A19)*(dataIntentos[Intento]=B19)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>39.191835884530846</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <f>COUNTIFS(dataIntentos[Nivel],A20,dataIntentos[Intento],B20, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A20,dataIntentos[Intento],B20, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.25</v>
+      </c>
+      <c r="E20" cm="1">
+        <f t="array" ref="E20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.0897247358851685</v>
+      </c>
+      <c r="F20">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.75</v>
+      </c>
+      <c r="G20" cm="1">
+        <f t="array" ref="G20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.299038105676658</v>
+      </c>
+      <c r="H20">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="I20" cm="1">
+        <f t="array" ref="I20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="J20">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="K20" cm="1">
+        <f t="array" ref="K20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="L20">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.25</v>
+      </c>
+      <c r="M20" cm="1">
+        <f t="array" ref="M20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="N20">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O20" cm="1">
+        <f t="array" ref="O20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="Q20" cm="1">
+        <f t="array" ref="Q20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="R20">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="S20" cm="1">
+        <f t="array" ref="S20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="T20">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="U20" cm="1">
+        <f t="array" ref="U20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="V20">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.75</v>
+      </c>
+      <c r="W20" cm="1">
+        <f t="array" ref="W20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="X20">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Y20" cm="1">
+        <f t="array" ref="Y20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.2247448713915889</v>
+      </c>
+      <c r="Z20">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA20" cm="1">
+        <f t="array" ref="AA20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC20" cm="1">
+        <f t="array" ref="AC20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>192.285</v>
+      </c>
+      <c r="AE20" cm="1">
+        <f t="array" ref="AE20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>130.25277465950583</v>
+      </c>
+      <c r="AF20">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG20" cm="1">
+        <f t="array" ref="AG20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH20">
+        <f>COUNTIFS(dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <f>COUNTIFS(dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>75</v>
+      </c>
+      <c r="AK20" cm="1">
+        <f t="array" ref="AK20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>25</v>
+      </c>
+      <c r="AL20">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A20,dataIntentos[Intento],B20,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>25</v>
+      </c>
+      <c r="AM20" cm="1">
+        <f t="array" ref="AM20">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A20)*(dataIntentos[Intento]=B20)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <f>COUNTIFS(dataIntentos[Nivel],A21,dataIntentos[Intento],B21, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A21,dataIntentos[Intento],B21, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="E21" cm="1">
+        <f t="array" ref="E21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="F21">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="G21" cm="1">
+        <f t="array" ref="G21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="H21">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I21" cm="1">
+        <f t="array" ref="I21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="K21" cm="1">
+        <f t="array" ref="K21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="L21">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M21" cm="1">
+        <f t="array" ref="M21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="N21">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O21" cm="1">
+        <f t="array" ref="O21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q21" cm="1">
+        <f t="array" ref="Q21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="R21">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="S21" cm="1">
+        <f t="array" ref="S21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="T21">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="U21" cm="1">
+        <f t="array" ref="U21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W21" cm="1">
+        <f t="array" ref="W21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="X21">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="Y21" cm="1">
+        <f t="array" ref="Y21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="Z21">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" cm="1">
+        <f t="array" ref="AA21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC21" cm="1">
+        <f t="array" ref="AC21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>206.09933333333333</v>
+      </c>
+      <c r="AE21" cm="1">
+        <f t="array" ref="AE21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>9.028543047222831</v>
+      </c>
+      <c r="AF21">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AG21" cm="1">
+        <f t="array" ref="AG21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <f>COUNTIFS(dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <f>COUNTIFS(dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>100</v>
+      </c>
+      <c r="AK21" cm="1">
+        <f t="array" ref="AK21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A21,dataIntentos[Intento],B21,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AM21" cm="1">
+        <f t="array" ref="AM21">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A21)*(dataIntentos[Intento]=B21)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>11</v>
+      </c>
+      <c r="C22">
+        <f>COUNTIFS(dataIntentos[Nivel],A22,dataIntentos[Intento],B22, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A22,dataIntentos[Intento],B22, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="E22" cm="1">
+        <f t="array" ref="E22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="F22">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G22" cm="1">
+        <f t="array" ref="G22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="H22">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="I22" cm="1">
+        <f t="array" ref="I22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.81649658092772603</v>
+      </c>
+      <c r="J22">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="K22" cm="1">
+        <f t="array" ref="K22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="L22">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M22" cm="1">
+        <f t="array" ref="M22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="N22">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O22" cm="1">
+        <f t="array" ref="O22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="P22">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q22" cm="1">
+        <f t="array" ref="Q22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="R22">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="S22" cm="1">
+        <f t="array" ref="S22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U22" cm="1">
+        <f t="array" ref="U22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="V22">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="W22" cm="1">
+        <f t="array" ref="W22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="X22">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="Y22" cm="1">
+        <f t="array" ref="Y22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.247219128924647</v>
+      </c>
+      <c r="Z22">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA22" cm="1">
+        <f t="array" ref="AA22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="AB22">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AC22" cm="1">
+        <f t="array" ref="AC22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="AD22">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>157.93833333333333</v>
+      </c>
+      <c r="AE22" cm="1">
+        <f t="array" ref="AE22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>99.431510345340499</v>
+      </c>
+      <c r="AF22">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="AG22" cm="1">
+        <f t="array" ref="AG22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>31.180478223116179</v>
+      </c>
+      <c r="AH22">
+        <f>COUNTIFS(dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <f>COUNTIFS(dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="AK22" cm="1">
+        <f t="array" ref="AK22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>23.570226039551585</v>
+      </c>
+      <c r="AL22">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A22,dataIntentos[Intento],B22,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="AM22" cm="1">
+        <f t="array" ref="AM22">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A22)*(dataIntentos[Intento]=B22)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>23.570226039551585</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <f>COUNTIFS(dataIntentos[Nivel],A23,dataIntentos[Intento],B23, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>39</v>
+      </c>
+      <c r="D23">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A23,dataIntentos[Intento],B23, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.7179487179487181</v>
+      </c>
+      <c r="E23" cm="1">
+        <f t="array" ref="E23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.7679296590705844</v>
+      </c>
+      <c r="F23">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="G23" cm="1">
+        <f t="array" ref="G23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.6794382455192631</v>
+      </c>
+      <c r="H23">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.71794871794871795</v>
+      </c>
+      <c r="I23" cm="1">
+        <f t="array" ref="I23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.78278653961403832</v>
+      </c>
+      <c r="J23">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.7692307692307692</v>
+      </c>
+      <c r="K23" cm="1">
+        <f t="array" ref="K23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.5292248061679562</v>
+      </c>
+      <c r="L23">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6923076923076923</v>
+      </c>
+      <c r="M23" cm="1">
+        <f t="array" ref="M23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.60569291338552389</v>
+      </c>
+      <c r="N23">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="O23" cm="1">
+        <f t="array" ref="O23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.26646935501059649</v>
+      </c>
+      <c r="P23">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.9487179487179487</v>
+      </c>
+      <c r="Q23" cm="1">
+        <f t="array" ref="Q23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.5516528482468994</v>
+      </c>
+      <c r="R23">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.3076923076923077</v>
+      </c>
+      <c r="S23" cm="1">
+        <f t="array" ref="S23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.3987878663575237</v>
+      </c>
+      <c r="T23">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.64102564102564108</v>
+      </c>
+      <c r="U23" cm="1">
+        <f t="array" ref="U23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.76751946395362902</v>
+      </c>
+      <c r="V23">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.4615384615384617</v>
+      </c>
+      <c r="W23" cm="1">
+        <f t="array" ref="W23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.0339407771105615</v>
+      </c>
+      <c r="X23">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.7692307692307692</v>
+      </c>
+      <c r="Y23" cm="1">
+        <f t="array" ref="Y23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0732538223823769</v>
+      </c>
+      <c r="Z23">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" cm="1">
+        <f t="array" ref="AA23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.128205128205128E-2</v>
+      </c>
+      <c r="AC23" cm="1">
+        <f t="array" ref="AC23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.22057244274468274</v>
+      </c>
+      <c r="AD23">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>190.16325641025637</v>
+      </c>
+      <c r="AE23" cm="1">
+        <f t="array" ref="AE23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>81.595655560794484</v>
+      </c>
+      <c r="AF23">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.897435897435898</v>
+      </c>
+      <c r="AG23" cm="1">
+        <f t="array" ref="AG23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>13.628392067608525</v>
+      </c>
+      <c r="AH23">
+        <f>COUNTIFS(dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>26</v>
+      </c>
+      <c r="AI23">
+        <f>COUNTIFS(dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9</v>
+      </c>
+      <c r="AJ23">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>78.13575313575312</v>
+      </c>
+      <c r="AK23" cm="1">
+        <f t="array" ref="AK23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>24.298530417398119</v>
+      </c>
+      <c r="AL23">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A23,dataIntentos[Intento],B23,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>21.864246864246859</v>
+      </c>
+      <c r="AM23" cm="1">
+        <f t="array" ref="AM23">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A23)*(dataIntentos[Intento]=B23)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>24.298530417398091</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <f>COUNTIFS(dataIntentos[Nivel],A24,dataIntentos[Intento],B24, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>24</v>
+      </c>
+      <c r="D24">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A24,dataIntentos[Intento],B24, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="E24" cm="1">
+        <f t="array" ref="E24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>3.0776975521032313</v>
+      </c>
+      <c r="F24">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.416666666666667</v>
+      </c>
+      <c r="G24" cm="1">
+        <f t="array" ref="G24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.396467307424734</v>
+      </c>
+      <c r="H24">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.75</v>
+      </c>
+      <c r="I24" cm="1">
+        <f t="array" ref="I24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.2665570127975554</v>
+      </c>
+      <c r="J24">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.0416666666666665</v>
+      </c>
+      <c r="K24" cm="1">
+        <f t="array" ref="K24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.67571978084278561</v>
+      </c>
+      <c r="L24">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.0416666666666665</v>
+      </c>
+      <c r="M24" cm="1">
+        <f t="array" ref="M24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.67571978084278561</v>
+      </c>
+      <c r="N24">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O24" cm="1">
+        <f t="array" ref="O24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.125</v>
+      </c>
+      <c r="Q24" cm="1">
+        <f t="array" ref="Q24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.7433632035635869</v>
+      </c>
+      <c r="R24">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.375</v>
+      </c>
+      <c r="S24" cm="1">
+        <f t="array" ref="S24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>2.2325713874364688</v>
+      </c>
+      <c r="T24">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.75</v>
+      </c>
+      <c r="U24" cm="1">
+        <f t="array" ref="U24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.2665570127975554</v>
+      </c>
+      <c r="V24">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.7916666666666665</v>
+      </c>
+      <c r="W24" cm="1">
+        <f t="array" ref="W24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.57584479004521882</v>
+      </c>
+      <c r="X24">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="Y24" cm="1">
+        <f t="array" ref="Y24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.6454972243679028</v>
+      </c>
+      <c r="Z24">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AA24" cm="1">
+        <f t="array" ref="AA24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.19982631347136331</v>
+      </c>
+      <c r="AB24">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AC24" cm="1">
+        <f t="array" ref="AC24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.19982631347136331</v>
+      </c>
+      <c r="AD24">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>176.38150000000005</v>
+      </c>
+      <c r="AE24" cm="1">
+        <f t="array" ref="AE24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>94.382527848555355</v>
+      </c>
+      <c r="AF24">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG24" cm="1">
+        <f t="array" ref="AG24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>14.433756729740644</v>
+      </c>
+      <c r="AH24">
+        <f>COUNTIFS(dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>15</v>
+      </c>
+      <c r="AI24">
+        <f>COUNTIFS(dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>10</v>
+      </c>
+      <c r="AJ24">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.590277777777757</v>
+      </c>
+      <c r="AK24" cm="1">
+        <f t="array" ref="AK24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>17.304595512428691</v>
+      </c>
+      <c r="AL24">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A24,dataIntentos[Intento],B24,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>14.409722222222213</v>
+      </c>
+      <c r="AM24" cm="1">
+        <f t="array" ref="AM24">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A24)*(dataIntentos[Intento]=B24)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>17.304595512428637</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <f>COUNTIFS(dataIntentos[Nivel],A25,dataIntentos[Intento],B25, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>13</v>
+      </c>
+      <c r="D25">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A25,dataIntentos[Intento],B25, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3076923076923075</v>
+      </c>
+      <c r="E25" cm="1">
+        <f t="array" ref="E25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1.4349813927828945</v>
+      </c>
+      <c r="F25">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6923076923076925</v>
+      </c>
+      <c r="G25" cm="1">
+        <f t="array" ref="G25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>1.3234346564680965</v>
+      </c>
+      <c r="H25">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="I25" cm="1">
+        <f t="array" ref="I25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.62492603112584311</v>
+      </c>
+      <c r="J25">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6923076923076923</v>
+      </c>
+      <c r="K25" cm="1">
+        <f t="array" ref="K25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="L25">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6153846153846154</v>
+      </c>
+      <c r="M25" cm="1">
+        <f t="array" ref="M25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.62492603112584311</v>
+      </c>
+      <c r="N25">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="O25" cm="1">
+        <f t="array" ref="O25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0.26646935501059649</v>
+      </c>
+      <c r="P25">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.6153846153846154</v>
+      </c>
+      <c r="Q25" cm="1">
+        <f t="array" ref="Q25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="R25">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="S25" cm="1">
+        <f t="array" ref="S25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.91664425290869112</v>
+      </c>
+      <c r="T25">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="U25" cm="1">
+        <f t="array" ref="U25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.63432394240271706</v>
+      </c>
+      <c r="V25">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3846153846153846</v>
+      </c>
+      <c r="W25" cm="1">
+        <f t="array" ref="W25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>1.2113858267710478</v>
+      </c>
+      <c r="X25">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6153846153846154</v>
+      </c>
+      <c r="Y25" cm="1">
+        <f t="array" ref="Y25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="Z25">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="AA25" cm="1">
+        <f t="array" ref="AA25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0.26646935501059649</v>
+      </c>
+      <c r="AB25">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AC25" cm="1">
+        <f t="array" ref="AC25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0.53293871002119297</v>
+      </c>
+      <c r="AD25">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>215.25384615384613</v>
+      </c>
+      <c r="AE25" cm="1">
+        <f t="array" ref="AE25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>246.84119872340418</v>
+      </c>
+      <c r="AF25">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>84.615384615384613</v>
+      </c>
+      <c r="AG25" cm="1">
+        <f t="array" ref="AG25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>15.623150778146078</v>
+      </c>
+      <c r="AH25">
+        <f>COUNTIFS(dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7</v>
+      </c>
+      <c r="AI25">
+        <f>COUNTIFS(dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ25">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>79.230769230769226</v>
+      </c>
+      <c r="AK25" cm="1">
+        <f t="array" ref="AK25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>27.639431950631383</v>
+      </c>
+      <c r="AL25">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A25,dataIntentos[Intento],B25,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>20.769230769230759</v>
+      </c>
+      <c r="AM25" cm="1">
+        <f t="array" ref="AM25">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A25)*(dataIntentos[Intento]=B25)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>27.639431950631383</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <f>COUNTIFS(dataIntentos[Nivel],A26,dataIntentos[Intento],B26, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A26,dataIntentos[Intento],B26, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="E26" cm="1">
+        <f t="array" ref="E26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>3.7416573867739413</v>
+      </c>
+      <c r="F26">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4.1111111111111107</v>
+      </c>
+      <c r="G26" cm="1">
+        <f t="array" ref="G26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>2.6851213274654606</v>
+      </c>
+      <c r="H26">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="I26" cm="1">
+        <f t="array" ref="I26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>1.1967032904743342</v>
+      </c>
+      <c r="J26">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8888888888888888</v>
+      </c>
+      <c r="K26" cm="1">
+        <f t="array" ref="K26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.99380798999990649</v>
+      </c>
+      <c r="L26">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.8888888888888888</v>
+      </c>
+      <c r="M26" cm="1">
+        <f t="array" ref="M26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.99380798999990649</v>
+      </c>
+      <c r="N26">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O26" cm="1">
+        <f t="array" ref="O26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="Q26" cm="1">
+        <f t="array" ref="Q26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>2.922876986214646</v>
+      </c>
+      <c r="R26">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="S26" cm="1">
+        <f t="array" ref="S26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>1.9309052441091963</v>
+      </c>
+      <c r="T26">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="U26" cm="1">
+        <f t="array" ref="U26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>1.1967032904743342</v>
+      </c>
+      <c r="V26">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.8888888888888888</v>
+      </c>
+      <c r="W26" cm="1">
+        <f t="array" ref="W26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.31426968052735449</v>
+      </c>
+      <c r="X26">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="Y26" cm="1">
+        <f t="array" ref="Y26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.56655772373253166</v>
+      </c>
+      <c r="Z26">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA26" cm="1">
+        <f t="array" ref="AA26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC26" cm="1">
+        <f t="array" ref="AC26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>161.08333333333337</v>
+      </c>
+      <c r="AE26" cm="1">
+        <f t="array" ref="AE26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>58.678472456070018</v>
+      </c>
+      <c r="AF26">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>86.111111111111114</v>
+      </c>
+      <c r="AG26" cm="1">
+        <f t="array" ref="AG26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.422599874998832</v>
+      </c>
+      <c r="AH26">
+        <f>COUNTIFS(dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="AI26">
+        <f>COUNTIFS(dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="AJ26">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>85.925925925925924</v>
+      </c>
+      <c r="AK26" cm="1">
+        <f t="array" ref="AK26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>13.196312408385063</v>
+      </c>
+      <c r="AL26">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A26,dataIntentos[Intento],B26,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>14.074074074074055</v>
+      </c>
+      <c r="AM26" cm="1">
+        <f t="array" ref="AM26">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A26)*(dataIntentos[Intento]=B26)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>13.196312408385074</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <f>COUNTIFS(dataIntentos[Nivel],A27,dataIntentos[Intento],B27, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A27,dataIntentos[Intento],B27, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="E27" cm="1">
+        <f t="array" ref="E27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>0.82915619758884995</v>
+      </c>
+      <c r="F27">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="G27" cm="1">
+        <f t="array" ref="G27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="H27">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.25</v>
+      </c>
+      <c r="I27" cm="1">
+        <f t="array" ref="I27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="J27">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="K27" cm="1">
+        <f t="array" ref="K27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="L27">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="M27" cm="1">
+        <f t="array" ref="M27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="N27">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O27" cm="1">
+        <f t="array" ref="O27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.75</v>
+      </c>
+      <c r="Q27" cm="1">
+        <f t="array" ref="Q27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="R27">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S27" cm="1">
+        <f t="array" ref="S27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="T27">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.25</v>
+      </c>
+      <c r="U27" cm="1">
+        <f t="array" ref="U27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="V27">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="W27" cm="1">
+        <f t="array" ref="W27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.25</v>
+      </c>
+      <c r="Y27" cm="1">
+        <f t="array" ref="Y27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.4330127018922193</v>
+      </c>
+      <c r="Z27">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" cm="1">
+        <f t="array" ref="AA27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC27" cm="1">
+        <f t="array" ref="AC27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>300.40100000000001</v>
+      </c>
+      <c r="AE27" cm="1">
+        <f t="array" ref="AE27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>194.8787775528674</v>
+      </c>
+      <c r="AF27">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.75</v>
+      </c>
+      <c r="AG27" cm="1">
+        <f t="array" ref="AG27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>10.825317547305483</v>
+      </c>
+      <c r="AH27">
+        <f>COUNTIFS(dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI27">
+        <f>COUNTIFS(dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ27">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>93.75</v>
+      </c>
+      <c r="AK27" cm="1">
+        <f t="array" ref="AK27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>10.825317547305483</v>
+      </c>
+      <c r="AL27">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A27,dataIntentos[Intento],B27,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>6.25</v>
+      </c>
+      <c r="AM27" cm="1">
+        <f t="array" ref="AM27">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A27)*(dataIntentos[Intento]=B27)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>10.825317547305483</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <f>COUNTIFS(dataIntentos[Nivel],A28,dataIntentos[Intento],B28, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A28,dataIntentos[Intento],B28, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="E28" cm="1">
+        <f t="array" ref="E28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>4.9216076867444665</v>
+      </c>
+      <c r="F28">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>8</v>
+      </c>
+      <c r="G28" cm="1">
+        <f t="array" ref="G28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>3.5590260840104371</v>
+      </c>
+      <c r="H28">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I28" cm="1">
+        <f t="array" ref="I28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>2.6246692913372702</v>
+      </c>
+      <c r="J28">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="K28" cm="1">
+        <f t="array" ref="K28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="L28">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="M28" cm="1">
+        <f t="array" ref="M28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="N28">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O28" cm="1">
+        <f t="array" ref="O28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="Q28" cm="1">
+        <f t="array" ref="Q28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>3.858612300930075</v>
+      </c>
+      <c r="R28">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>5</v>
+      </c>
+      <c r="S28" cm="1">
+        <f t="array" ref="S28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>3.2659863237109041</v>
+      </c>
+      <c r="T28">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="U28" cm="1">
+        <f t="array" ref="U28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>2.6246692913372702</v>
+      </c>
+      <c r="V28">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="W28" cm="1">
+        <f t="array" ref="W28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0.94280904158206336</v>
+      </c>
+      <c r="X28">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="Y28" cm="1">
+        <f t="array" ref="Y28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.47140452079103168</v>
+      </c>
+      <c r="Z28">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA28" cm="1">
+        <f t="array" ref="AA28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC28" cm="1">
+        <f t="array" ref="AC28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>323.9736666666667</v>
+      </c>
+      <c r="AE28" cm="1">
+        <f t="array" ref="AE28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>166.16940076587176</v>
+      </c>
+      <c r="AF28">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>83.333333333333329</v>
+      </c>
+      <c r="AG28" cm="1">
+        <f t="array" ref="AG28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>11.785113019775793</v>
+      </c>
+      <c r="AH28">
+        <f>COUNTIFS(dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI28">
+        <f>COUNTIFS(dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AJ28">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>79.166666666666671</v>
+      </c>
+      <c r="AK28" cm="1">
+        <f t="array" ref="AK28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>15.590239111558089</v>
+      </c>
+      <c r="AL28">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A28,dataIntentos[Intento],B28,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AM28" cm="1">
+        <f t="array" ref="AM28">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A28)*(dataIntentos[Intento]=B28)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>15.590239111558089</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <f>COUNTIFS(dataIntentos[Nivel],A29,dataIntentos[Intento],B29, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <f>AVERAGEIFS(dataIntentos[Pasos planificados],dataIntentos[Nivel],A29,dataIntentos[Intento],B29, dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="E29" cm="1">
+        <f t="array" ref="E29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos planificados]))</f>
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <f>AVERAGEIFS(dataIntentos[Pasos ejecutados],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5</v>
+      </c>
+      <c r="G29" cm="1">
+        <f t="array" ref="G29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Pasos ejecutados]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="H29">
+        <f>AVERAGEIFS(dataIntentos[Errores ejecucion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="I29" cm="1">
+        <f t="array" ref="I29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29*(dataIntentos[Pasos planificados]&lt;&gt;0)),dataIntentos[Errores ejecucion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="J29">
+        <f>AVERAGEIFS(dataIntentos[Num dormir planificado],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="K29" cm="1">
+        <f t="array" ref="K29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num dormir planificado]))</f>
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <f>AVERAGEIFS(dataIntentos[Correctos dormir],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="M29" cm="1">
+        <f t="array" ref="M29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <f>AVERAGEIFS(dataIntentos[Errores dormir],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="O29" cm="1">
+        <f t="array" ref="O29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores dormir]))</f>
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <f>AVERAGEIFS(dataIntentos[Num ubicacion planificado],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="Q29" cm="1">
+        <f t="array" ref="Q29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num ubicacion planificado]))</f>
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <f>AVERAGEIFS(dataIntentos[Correctos ubicacion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1.5</v>
+      </c>
+      <c r="S29" cm="1">
+        <f t="array" ref="S29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Correctos ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="T29">
+        <f>AVERAGEIFS(dataIntentos[Errores ubicacion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0.5</v>
+      </c>
+      <c r="U29" cm="1">
+        <f t="array" ref="U29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores ubicacion]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="V29">
+        <f>AVERAGEIFS(dataIntentos[Paradas posibles],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>4</v>
+      </c>
+      <c r="W29" cm="1">
+        <f t="array" ref="W29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas posibles]))</f>
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <f>AVERAGEIFS(dataIntentos[Paradas realizadas],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>3.5</v>
+      </c>
+      <c r="Y29" cm="1">
+        <f t="array" ref="Y29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Paradas realizadas]))</f>
+        <v>0.5</v>
+      </c>
+      <c r="Z29">
+        <f>AVERAGEIFS(dataIntentos[Errores parada por tiempo excedido],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AA29" cm="1">
+        <f t="array" ref="AA29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Errores parada por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <f>AVERAGEIFS(dataIntentos[Num errores por tiempo excedido],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AC29" cm="1">
+        <f t="array" ref="AC29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Num errores por tiempo excedido]))</f>
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <f>AVERAGEIFS(dataIntentos[Tiempo duracion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>107.14150000000001</v>
+      </c>
+      <c r="AE29" cm="1">
+        <f t="array" ref="AE29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[Tiempo duracion]))</f>
+        <v>17.634499999999949</v>
+      </c>
+      <c r="AF29">
+        <f>AVERAGEIFS(dataIntentos[%Reglas respetadas ejecucion],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>87.5</v>
+      </c>
+      <c r="AG29" cm="1">
+        <f t="array" ref="AG29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[%Reglas respetadas ejecucion]))</f>
+        <v>12.5</v>
+      </c>
+      <c r="AH29">
+        <f>COUNTIFS(dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Reglas planificacion cumplidas],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>1</v>
+      </c>
+      <c r="AI29">
+        <f>COUNTIFS(dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Completado],"VERDADERO",dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <f>AVERAGEIFS(dataIntentos[% Aciertos],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>90</v>
+      </c>
+      <c r="AK29" cm="1">
+        <f t="array" ref="AK29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Aciertos]))</f>
+        <v>10</v>
+      </c>
+      <c r="AL29">
+        <f>AVERAGEIFS(dataIntentos[% Mal],dataIntentos[Nivel],A29,dataIntentos[Intento],B29,dataIntentos[Pasos planificados],"&gt;0")</f>
+        <v>10</v>
+      </c>
+      <c r="AM29" cm="1">
+        <f t="array" ref="AM29">_xlfn.STDEV.P(IF((dataIntentos[Nivel]=A29)*(dataIntentos[Intento]=B29)*(dataIntentos[Pasos planificados]&lt;&gt;0),dataIntentos[% Mal]))</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
